--- a/data/exports/relationship_validation.xlsx
+++ b/data/exports/relationship_validation.xlsx
@@ -1987,10 +1987,10 @@
     <t>open</t>
   </si>
   <si>
-    <t>2026-05-23 23:20:27</t>
-  </si>
-  <si>
-    <t>2026-05-23 23:20:26</t>
+    <t>2026-05-23 23:28:23</t>
+  </si>
+  <si>
+    <t>2026-05-23 23:28:22</t>
   </si>
 </sst>
 </file>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>396</v>
+        <v>596</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -2386,7 +2386,7 @@
         <v>201</v>
       </c>
       <c r="H2">
-        <v>119335</v>
+        <v>130207</v>
       </c>
       <c r="J2" t="s">
         <v>515</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>397</v>
+        <v>597</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -2421,7 +2421,7 @@
         <v>201</v>
       </c>
       <c r="H3">
-        <v>119343</v>
+        <v>130215</v>
       </c>
       <c r="J3" t="s">
         <v>515</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>327</v>
+        <v>527</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -2456,7 +2456,7 @@
         <v>446</v>
       </c>
       <c r="H4">
-        <v>110589</v>
+        <v>121461</v>
       </c>
       <c r="J4" t="s">
         <v>516</v>
@@ -2465,12 +2465,12 @@
         <v>656</v>
       </c>
       <c r="L4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>385</v>
+        <v>585</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -2491,7 +2491,7 @@
         <v>447</v>
       </c>
       <c r="H5">
-        <v>118943</v>
+        <v>129815</v>
       </c>
       <c r="J5" t="s">
         <v>517</v>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2526,7 +2526,7 @@
         <v>208</v>
       </c>
       <c r="H6">
-        <v>109181</v>
+        <v>120053</v>
       </c>
       <c r="J6" t="s">
         <v>518</v>
@@ -2535,12 +2535,12 @@
         <v>656</v>
       </c>
       <c r="L6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>318</v>
+        <v>518</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2561,7 +2561,7 @@
         <v>208</v>
       </c>
       <c r="H7">
-        <v>109179</v>
+        <v>120051</v>
       </c>
       <c r="J7" t="s">
         <v>519</v>
@@ -2570,12 +2570,12 @@
         <v>656</v>
       </c>
       <c r="L7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>332</v>
+        <v>532</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -2596,7 +2596,7 @@
         <v>448</v>
       </c>
       <c r="H8">
-        <v>111829</v>
+        <v>122701</v>
       </c>
       <c r="J8" t="s">
         <v>520</v>
@@ -2605,12 +2605,12 @@
         <v>656</v>
       </c>
       <c r="L8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>370</v>
+        <v>570</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -2631,7 +2631,7 @@
         <v>449</v>
       </c>
       <c r="H9">
-        <v>117101</v>
+        <v>127973</v>
       </c>
       <c r="J9" t="s">
         <v>521</v>
@@ -2640,12 +2640,12 @@
         <v>656</v>
       </c>
       <c r="L9" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>215</v>
+        <v>415</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>349</v>
+        <v>549</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2692,7 +2692,7 @@
         <v>450</v>
       </c>
       <c r="H11">
-        <v>114979</v>
+        <v>125851</v>
       </c>
       <c r="J11" t="s">
         <v>523</v>
@@ -2701,12 +2701,12 @@
         <v>656</v>
       </c>
       <c r="L11" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2727,7 +2727,7 @@
         <v>451</v>
       </c>
       <c r="H12">
-        <v>114983</v>
+        <v>125855</v>
       </c>
       <c r="J12" t="s">
         <v>524</v>
@@ -2736,12 +2736,12 @@
         <v>656</v>
       </c>
       <c r="L12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>351</v>
+        <v>551</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -2762,7 +2762,7 @@
         <v>452</v>
       </c>
       <c r="H13">
-        <v>114987</v>
+        <v>125859</v>
       </c>
       <c r="J13" t="s">
         <v>525</v>
@@ -2771,12 +2771,12 @@
         <v>656</v>
       </c>
       <c r="L13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>352</v>
+        <v>552</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2797,7 +2797,7 @@
         <v>453</v>
       </c>
       <c r="H14">
-        <v>114991</v>
+        <v>125863</v>
       </c>
       <c r="J14" t="s">
         <v>526</v>
@@ -2806,12 +2806,12 @@
         <v>656</v>
       </c>
       <c r="L14" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>353</v>
+        <v>553</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2832,7 +2832,7 @@
         <v>454</v>
       </c>
       <c r="H15">
-        <v>114995</v>
+        <v>125867</v>
       </c>
       <c r="J15" t="s">
         <v>527</v>
@@ -2841,12 +2841,12 @@
         <v>656</v>
       </c>
       <c r="L15" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>362</v>
+        <v>562</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -2867,7 +2867,7 @@
         <v>455</v>
       </c>
       <c r="H16">
-        <v>116833</v>
+        <v>127705</v>
       </c>
       <c r="J16" t="s">
         <v>528</v>
@@ -2876,12 +2876,12 @@
         <v>656</v>
       </c>
       <c r="L16" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17">
-        <v>363</v>
+        <v>563</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -2902,7 +2902,7 @@
         <v>456</v>
       </c>
       <c r="H17">
-        <v>116837</v>
+        <v>127709</v>
       </c>
       <c r="J17" t="s">
         <v>529</v>
@@ -2911,12 +2911,12 @@
         <v>656</v>
       </c>
       <c r="L17" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18">
-        <v>364</v>
+        <v>564</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -2937,7 +2937,7 @@
         <v>457</v>
       </c>
       <c r="H18">
-        <v>116841</v>
+        <v>127713</v>
       </c>
       <c r="J18" t="s">
         <v>530</v>
@@ -2946,12 +2946,12 @@
         <v>656</v>
       </c>
       <c r="L18" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19">
-        <v>365</v>
+        <v>565</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -2972,7 +2972,7 @@
         <v>458</v>
       </c>
       <c r="H19">
-        <v>116845</v>
+        <v>127717</v>
       </c>
       <c r="J19" t="s">
         <v>531</v>
@@ -2981,12 +2981,12 @@
         <v>656</v>
       </c>
       <c r="L19" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20">
-        <v>366</v>
+        <v>566</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3007,7 +3007,7 @@
         <v>459</v>
       </c>
       <c r="H20">
-        <v>116849</v>
+        <v>127721</v>
       </c>
       <c r="J20" t="s">
         <v>532</v>
@@ -3016,12 +3016,12 @@
         <v>656</v>
       </c>
       <c r="L20" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21">
-        <v>367</v>
+        <v>567</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3042,7 +3042,7 @@
         <v>460</v>
       </c>
       <c r="H21">
-        <v>116853</v>
+        <v>127725</v>
       </c>
       <c r="J21" t="s">
         <v>533</v>
@@ -3051,12 +3051,12 @@
         <v>656</v>
       </c>
       <c r="L21" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22">
-        <v>324</v>
+        <v>524</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3077,7 +3077,7 @@
         <v>461</v>
       </c>
       <c r="H22">
-        <v>109847</v>
+        <v>120719</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -3089,12 +3089,12 @@
         <v>656</v>
       </c>
       <c r="L22" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23">
-        <v>330</v>
+        <v>530</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3115,7 +3115,7 @@
         <v>462</v>
       </c>
       <c r="H23">
-        <v>111641</v>
+        <v>122513</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -3127,12 +3127,12 @@
         <v>656</v>
       </c>
       <c r="L23" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24">
-        <v>340</v>
+        <v>540</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -3153,7 +3153,7 @@
         <v>463</v>
       </c>
       <c r="H24">
-        <v>113029</v>
+        <v>123901</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -3165,12 +3165,12 @@
         <v>656</v>
       </c>
       <c r="L24" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25">
-        <v>339</v>
+        <v>539</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -3191,7 +3191,7 @@
         <v>464</v>
       </c>
       <c r="H25">
-        <v>112885</v>
+        <v>123757</v>
       </c>
       <c r="I25">
         <v>8</v>
@@ -3203,12 +3203,12 @@
         <v>656</v>
       </c>
       <c r="L25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26">
-        <v>348</v>
+        <v>548</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3229,7 +3229,7 @@
         <v>465</v>
       </c>
       <c r="H26">
-        <v>114249</v>
+        <v>125121</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -3241,12 +3241,12 @@
         <v>656</v>
       </c>
       <c r="L26" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27">
-        <v>393</v>
+        <v>593</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
@@ -3267,7 +3267,7 @@
         <v>466</v>
       </c>
       <c r="H27">
-        <v>119277</v>
+        <v>130149</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28">
-        <v>347</v>
+        <v>547</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3305,7 +3305,7 @@
         <v>465</v>
       </c>
       <c r="H28">
-        <v>114247</v>
+        <v>125119</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -3317,12 +3317,12 @@
         <v>656</v>
       </c>
       <c r="L28" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29">
-        <v>374</v>
+        <v>574</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -3343,7 +3343,7 @@
         <v>467</v>
       </c>
       <c r="H29">
-        <v>118139</v>
+        <v>129011</v>
       </c>
       <c r="I29">
         <v>9</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30">
-        <v>314</v>
+        <v>514</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -3381,7 +3381,7 @@
         <v>468</v>
       </c>
       <c r="H30">
-        <v>108847</v>
+        <v>119719</v>
       </c>
       <c r="I30">
         <v>9</v>
@@ -3393,12 +3393,12 @@
         <v>656</v>
       </c>
       <c r="L30" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31">
-        <v>354</v>
+        <v>554</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -3419,7 +3419,7 @@
         <v>469</v>
       </c>
       <c r="H31">
-        <v>115133</v>
+        <v>126005</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -3431,12 +3431,12 @@
         <v>656</v>
       </c>
       <c r="L31" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32">
-        <v>346</v>
+        <v>546</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -3457,7 +3457,7 @@
         <v>470</v>
       </c>
       <c r="H32">
-        <v>114207</v>
+        <v>125079</v>
       </c>
       <c r="I32">
         <v>9</v>
@@ -3469,12 +3469,12 @@
         <v>656</v>
       </c>
       <c r="L32" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33">
-        <v>381</v>
+        <v>581</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -3495,7 +3495,7 @@
         <v>470</v>
       </c>
       <c r="H33">
-        <v>118725</v>
+        <v>129597</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34">
-        <v>373</v>
+        <v>573</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -3533,7 +3533,7 @@
         <v>467</v>
       </c>
       <c r="H34">
-        <v>118137</v>
+        <v>129009</v>
       </c>
       <c r="I34">
         <v>9</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35">
-        <v>325</v>
+        <v>525</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -3571,7 +3571,7 @@
         <v>471</v>
       </c>
       <c r="H35">
-        <v>110349</v>
+        <v>121221</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -3583,12 +3583,12 @@
         <v>656</v>
       </c>
       <c r="L35" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36">
-        <v>345</v>
+        <v>545</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -3609,7 +3609,7 @@
         <v>470</v>
       </c>
       <c r="H36">
-        <v>114205</v>
+        <v>125077</v>
       </c>
       <c r="I36">
         <v>9</v>
@@ -3621,12 +3621,12 @@
         <v>656</v>
       </c>
       <c r="L36" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37">
-        <v>402</v>
+        <v>602</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3647,7 +3647,7 @@
         <v>472</v>
       </c>
       <c r="H37">
-        <v>119519</v>
+        <v>130391</v>
       </c>
       <c r="I37">
         <v>10</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38">
-        <v>372</v>
+        <v>572</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -3685,7 +3685,7 @@
         <v>473</v>
       </c>
       <c r="H38">
-        <v>118115</v>
+        <v>128987</v>
       </c>
       <c r="I38">
         <v>11</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39">
-        <v>344</v>
+        <v>544</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -3723,7 +3723,7 @@
         <v>474</v>
       </c>
       <c r="H39">
-        <v>113663</v>
+        <v>124535</v>
       </c>
       <c r="I39">
         <v>11</v>
@@ -3735,12 +3735,12 @@
         <v>656</v>
       </c>
       <c r="L39" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40">
-        <v>360</v>
+        <v>560</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -3761,7 +3761,7 @@
         <v>475</v>
       </c>
       <c r="H40">
-        <v>115641</v>
+        <v>126513</v>
       </c>
       <c r="I40">
         <v>11</v>
@@ -3773,12 +3773,12 @@
         <v>656</v>
       </c>
       <c r="L40" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41">
-        <v>384</v>
+        <v>584</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -3799,7 +3799,7 @@
         <v>476</v>
       </c>
       <c r="H41">
-        <v>118889</v>
+        <v>129761</v>
       </c>
       <c r="I41">
         <v>11</v>
@@ -3816,7 +3816,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42">
-        <v>369</v>
+        <v>569</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
@@ -3837,7 +3837,7 @@
         <v>477</v>
       </c>
       <c r="H42">
-        <v>116999</v>
+        <v>127871</v>
       </c>
       <c r="I42">
         <v>12</v>
@@ -3849,12 +3849,12 @@
         <v>656</v>
       </c>
       <c r="L42" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43">
-        <v>321</v>
+        <v>521</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
@@ -3875,7 +3875,7 @@
         <v>478</v>
       </c>
       <c r="H43">
-        <v>109215</v>
+        <v>120087</v>
       </c>
       <c r="I43">
         <v>12</v>
@@ -3887,12 +3887,12 @@
         <v>656</v>
       </c>
       <c r="L43" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44">
-        <v>343</v>
+        <v>543</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
@@ -3913,7 +3913,7 @@
         <v>479</v>
       </c>
       <c r="H44">
-        <v>113561</v>
+        <v>124433</v>
       </c>
       <c r="I44">
         <v>12</v>
@@ -3925,12 +3925,12 @@
         <v>656</v>
       </c>
       <c r="L44" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45">
-        <v>368</v>
+        <v>568</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -3951,7 +3951,7 @@
         <v>480</v>
       </c>
       <c r="H45">
-        <v>116859</v>
+        <v>127731</v>
       </c>
       <c r="I45">
         <v>12</v>
@@ -3963,12 +3963,12 @@
         <v>656</v>
       </c>
       <c r="L45" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46">
-        <v>392</v>
+        <v>592</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -3989,7 +3989,7 @@
         <v>481</v>
       </c>
       <c r="H46">
-        <v>119201</v>
+        <v>130073</v>
       </c>
       <c r="I46">
         <v>13</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47">
-        <v>398</v>
+        <v>598</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -4027,7 +4027,7 @@
         <v>235</v>
       </c>
       <c r="H47">
-        <v>119375</v>
+        <v>130247</v>
       </c>
       <c r="I47">
         <v>13</v>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48">
-        <v>323</v>
+        <v>523</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4065,7 +4065,7 @@
         <v>482</v>
       </c>
       <c r="H48">
-        <v>109657</v>
+        <v>120529</v>
       </c>
       <c r="I48">
         <v>13</v>
@@ -4077,12 +4077,12 @@
         <v>656</v>
       </c>
       <c r="L48" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49">
-        <v>355</v>
+        <v>555</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
@@ -4103,7 +4103,7 @@
         <v>483</v>
       </c>
       <c r="H49">
-        <v>115245</v>
+        <v>126117</v>
       </c>
       <c r="I49">
         <v>13</v>
@@ -4115,12 +4115,12 @@
         <v>656</v>
       </c>
       <c r="L49" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50">
-        <v>328</v>
+        <v>528</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
@@ -4141,7 +4141,7 @@
         <v>484</v>
       </c>
       <c r="H50">
-        <v>110881</v>
+        <v>121753</v>
       </c>
       <c r="I50">
         <v>13</v>
@@ -4153,12 +4153,12 @@
         <v>656</v>
       </c>
       <c r="L50" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51">
-        <v>342</v>
+        <v>542</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
@@ -4179,7 +4179,7 @@
         <v>239</v>
       </c>
       <c r="H51">
-        <v>113527</v>
+        <v>124399</v>
       </c>
       <c r="I51">
         <v>13</v>
@@ -4191,12 +4191,12 @@
         <v>656</v>
       </c>
       <c r="L51" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52">
-        <v>387</v>
+        <v>587</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
@@ -4217,7 +4217,7 @@
         <v>485</v>
       </c>
       <c r="H52">
-        <v>119023</v>
+        <v>129895</v>
       </c>
       <c r="I52">
         <v>13</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53">
-        <v>386</v>
+        <v>586</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
@@ -4255,7 +4255,7 @@
         <v>486</v>
       </c>
       <c r="H53">
-        <v>118947</v>
+        <v>129819</v>
       </c>
       <c r="I53">
         <v>13</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54">
-        <v>401</v>
+        <v>601</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
@@ -4293,7 +4293,7 @@
         <v>487</v>
       </c>
       <c r="H54">
-        <v>119473</v>
+        <v>130345</v>
       </c>
       <c r="I54">
         <v>14</v>
@@ -4310,7 +4310,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55">
-        <v>358</v>
+        <v>558</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
@@ -4331,7 +4331,7 @@
         <v>488</v>
       </c>
       <c r="H55">
-        <v>115489</v>
+        <v>126361</v>
       </c>
       <c r="I55">
         <v>14</v>
@@ -4343,12 +4343,12 @@
         <v>656</v>
       </c>
       <c r="L55" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56">
-        <v>382</v>
+        <v>582</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
@@ -4369,7 +4369,7 @@
         <v>489</v>
       </c>
       <c r="H56">
-        <v>118781</v>
+        <v>129653</v>
       </c>
       <c r="I56">
         <v>14</v>
@@ -4386,7 +4386,7 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57">
-        <v>359</v>
+        <v>559</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
@@ -4407,7 +4407,7 @@
         <v>490</v>
       </c>
       <c r="H57">
-        <v>115541</v>
+        <v>126413</v>
       </c>
       <c r="I57">
         <v>14</v>
@@ -4419,12 +4419,12 @@
         <v>656</v>
       </c>
       <c r="L57" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58">
-        <v>333</v>
+        <v>533</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
@@ -4445,7 +4445,7 @@
         <v>491</v>
       </c>
       <c r="H58">
-        <v>112185</v>
+        <v>123057</v>
       </c>
       <c r="I58">
         <v>14</v>
@@ -4457,12 +4457,12 @@
         <v>656</v>
       </c>
       <c r="L58" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59">
-        <v>338</v>
+        <v>538</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
@@ -4483,7 +4483,7 @@
         <v>492</v>
       </c>
       <c r="H59">
-        <v>112869</v>
+        <v>123741</v>
       </c>
       <c r="I59">
         <v>14</v>
@@ -4495,12 +4495,12 @@
         <v>656</v>
       </c>
       <c r="L59" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60">
-        <v>331</v>
+        <v>531</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4521,7 +4521,7 @@
         <v>493</v>
       </c>
       <c r="H60">
-        <v>111735</v>
+        <v>122607</v>
       </c>
       <c r="I60">
         <v>14</v>
@@ -4533,12 +4533,12 @@
         <v>656</v>
       </c>
       <c r="L60" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61">
-        <v>334</v>
+        <v>534</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
@@ -4559,7 +4559,7 @@
         <v>491</v>
       </c>
       <c r="H61">
-        <v>112187</v>
+        <v>123059</v>
       </c>
       <c r="I61">
         <v>14</v>
@@ -4571,12 +4571,12 @@
         <v>656</v>
       </c>
       <c r="L61" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62">
-        <v>388</v>
+        <v>588</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
@@ -4597,7 +4597,7 @@
         <v>494</v>
       </c>
       <c r="H62">
-        <v>119047</v>
+        <v>129919</v>
       </c>
       <c r="I62">
         <v>14</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
@@ -4635,7 +4635,7 @@
         <v>251</v>
       </c>
       <c r="H63">
-        <v>118679</v>
+        <v>129551</v>
       </c>
       <c r="I63">
         <v>14</v>
@@ -4652,7 +4652,7 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64">
-        <v>371</v>
+        <v>571</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
@@ -4673,7 +4673,7 @@
         <v>495</v>
       </c>
       <c r="H64">
-        <v>117931</v>
+        <v>128803</v>
       </c>
       <c r="I64">
         <v>14</v>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65">
-        <v>357</v>
+        <v>557</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
@@ -4711,7 +4711,7 @@
         <v>496</v>
       </c>
       <c r="H65">
-        <v>115269</v>
+        <v>126141</v>
       </c>
       <c r="I65">
         <v>15</v>
@@ -4723,12 +4723,12 @@
         <v>656</v>
       </c>
       <c r="L65" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66">
-        <v>375</v>
+        <v>575</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
@@ -4749,7 +4749,7 @@
         <v>497</v>
       </c>
       <c r="H66">
-        <v>118237</v>
+        <v>129109</v>
       </c>
       <c r="I66">
         <v>15</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67">
-        <v>337</v>
+        <v>537</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
@@ -4787,7 +4787,7 @@
         <v>498</v>
       </c>
       <c r="H67">
-        <v>112839</v>
+        <v>123711</v>
       </c>
       <c r="I67">
         <v>15</v>
@@ -4799,12 +4799,12 @@
         <v>656</v>
       </c>
       <c r="L67" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68">
-        <v>322</v>
+        <v>522</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
@@ -4825,7 +4825,7 @@
         <v>499</v>
       </c>
       <c r="H68">
-        <v>109617</v>
+        <v>120489</v>
       </c>
       <c r="I68">
         <v>15</v>
@@ -4837,12 +4837,12 @@
         <v>656</v>
       </c>
       <c r="L68" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69">
-        <v>335</v>
+        <v>535</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -4863,7 +4863,7 @@
         <v>246</v>
       </c>
       <c r="H69">
-        <v>112231</v>
+        <v>123103</v>
       </c>
       <c r="I69">
         <v>15</v>
@@ -4875,12 +4875,12 @@
         <v>656</v>
       </c>
       <c r="L69" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70">
-        <v>326</v>
+        <v>526</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -4901,7 +4901,7 @@
         <v>500</v>
       </c>
       <c r="H70">
-        <v>110575</v>
+        <v>121447</v>
       </c>
       <c r="I70">
         <v>15</v>
@@ -4913,12 +4913,12 @@
         <v>656</v>
       </c>
       <c r="L70" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71">
-        <v>378</v>
+        <v>578</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
@@ -4939,7 +4939,7 @@
         <v>501</v>
       </c>
       <c r="H71">
-        <v>118583</v>
+        <v>129455</v>
       </c>
       <c r="I71">
         <v>15</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72">
-        <v>394</v>
+        <v>594</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
@@ -4977,7 +4977,7 @@
         <v>502</v>
       </c>
       <c r="H72">
-        <v>119297</v>
+        <v>130169</v>
       </c>
       <c r="I72">
         <v>15</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73">
-        <v>336</v>
+        <v>536</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
@@ -5015,7 +5015,7 @@
         <v>503</v>
       </c>
       <c r="H73">
-        <v>112663</v>
+        <v>123535</v>
       </c>
       <c r="I73">
         <v>15</v>
@@ -5027,12 +5027,12 @@
         <v>656</v>
       </c>
       <c r="L73" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74">
-        <v>390</v>
+        <v>590</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -5053,7 +5053,7 @@
         <v>504</v>
       </c>
       <c r="H74">
-        <v>119091</v>
+        <v>129963</v>
       </c>
       <c r="I74">
         <v>15</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75">
-        <v>356</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
@@ -5091,7 +5091,7 @@
         <v>496</v>
       </c>
       <c r="H75">
-        <v>115267</v>
+        <v>126139</v>
       </c>
       <c r="I75">
         <v>15</v>
@@ -5103,12 +5103,12 @@
         <v>656</v>
       </c>
       <c r="L75" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76">
-        <v>341</v>
+        <v>541</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
@@ -5129,7 +5129,7 @@
         <v>505</v>
       </c>
       <c r="H76">
-        <v>113361</v>
+        <v>124233</v>
       </c>
       <c r="I76">
         <v>15</v>
@@ -5141,12 +5141,12 @@
         <v>656</v>
       </c>
       <c r="L76" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77">
-        <v>361</v>
+        <v>561</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
@@ -5167,7 +5167,7 @@
         <v>506</v>
       </c>
       <c r="H77">
-        <v>115891</v>
+        <v>126763</v>
       </c>
       <c r="I77">
         <v>15</v>
@@ -5179,12 +5179,12 @@
         <v>656</v>
       </c>
       <c r="L77" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78">
-        <v>376</v>
+        <v>576</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
@@ -5205,7 +5205,7 @@
         <v>507</v>
       </c>
       <c r="H78">
-        <v>118417</v>
+        <v>129289</v>
       </c>
       <c r="I78">
         <v>16</v>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
@@ -5243,7 +5243,7 @@
         <v>508</v>
       </c>
       <c r="H79">
-        <v>119465</v>
+        <v>130337</v>
       </c>
       <c r="I79">
         <v>16</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80">
-        <v>399</v>
+        <v>599</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
@@ -5281,7 +5281,7 @@
         <v>509</v>
       </c>
       <c r="H80">
-        <v>119453</v>
+        <v>130325</v>
       </c>
       <c r="I80">
         <v>16</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81">
-        <v>383</v>
+        <v>583</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
@@ -5319,7 +5319,7 @@
         <v>510</v>
       </c>
       <c r="H81">
-        <v>118855</v>
+        <v>129727</v>
       </c>
       <c r="I81">
         <v>16</v>
@@ -5336,7 +5336,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82">
-        <v>379</v>
+        <v>579</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
@@ -5357,7 +5357,7 @@
         <v>267</v>
       </c>
       <c r="H82">
-        <v>118617</v>
+        <v>129489</v>
       </c>
       <c r="I82">
         <v>17</v>
@@ -5374,7 +5374,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83">
-        <v>391</v>
+        <v>591</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
@@ -5395,7 +5395,7 @@
         <v>511</v>
       </c>
       <c r="H83">
-        <v>119179</v>
+        <v>130051</v>
       </c>
       <c r="I83">
         <v>17</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84">
-        <v>395</v>
+        <v>595</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
@@ -5433,7 +5433,7 @@
         <v>511</v>
       </c>
       <c r="H84">
-        <v>119305</v>
+        <v>130177</v>
       </c>
       <c r="I84">
         <v>17</v>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85">
-        <v>389</v>
+        <v>589</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
@@ -5471,7 +5471,7 @@
         <v>267</v>
       </c>
       <c r="H85">
-        <v>119085</v>
+        <v>129957</v>
       </c>
       <c r="I85">
         <v>18</v>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86">
-        <v>275</v>
+        <v>475</v>
       </c>
       <c r="B86" t="s">
         <v>15</v>
@@ -5509,12 +5509,12 @@
         <v>656</v>
       </c>
       <c r="L86" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87">
-        <v>294</v>
+        <v>494</v>
       </c>
       <c r="B87" t="s">
         <v>15</v>
@@ -5535,12 +5535,12 @@
         <v>656</v>
       </c>
       <c r="L87" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88">
-        <v>316</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s">
         <v>16</v>
@@ -5561,7 +5561,7 @@
         <v>512</v>
       </c>
       <c r="H88">
-        <v>109065</v>
+        <v>119937</v>
       </c>
       <c r="J88" t="s">
         <v>557</v>
@@ -5570,12 +5570,12 @@
         <v>656</v>
       </c>
       <c r="L88" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89">
-        <v>303</v>
+        <v>503</v>
       </c>
       <c r="B89" t="s">
         <v>15</v>
@@ -5596,12 +5596,12 @@
         <v>656</v>
       </c>
       <c r="L89" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90">
-        <v>304</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s">
         <v>15</v>
@@ -5622,12 +5622,12 @@
         <v>656</v>
       </c>
       <c r="L90" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91">
-        <v>319</v>
+        <v>519</v>
       </c>
       <c r="B91" t="s">
         <v>16</v>
@@ -5648,7 +5648,7 @@
         <v>208</v>
       </c>
       <c r="H91">
-        <v>109181</v>
+        <v>120053</v>
       </c>
       <c r="J91" t="s">
         <v>560</v>
@@ -5657,12 +5657,12 @@
         <v>656</v>
       </c>
       <c r="L91" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92">
-        <v>258</v>
+        <v>458</v>
       </c>
       <c r="B92" t="s">
         <v>15</v>
@@ -5683,12 +5683,12 @@
         <v>656</v>
       </c>
       <c r="L92" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93">
-        <v>292</v>
+        <v>492</v>
       </c>
       <c r="B93" t="s">
         <v>15</v>
@@ -5709,12 +5709,12 @@
         <v>656</v>
       </c>
       <c r="L93" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94">
-        <v>287</v>
+        <v>487</v>
       </c>
       <c r="B94" t="s">
         <v>15</v>
@@ -5735,12 +5735,12 @@
         <v>656</v>
       </c>
       <c r="L94" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95">
-        <v>317</v>
+        <v>517</v>
       </c>
       <c r="B95" t="s">
         <v>16</v>
@@ -5761,7 +5761,7 @@
         <v>208</v>
       </c>
       <c r="H95">
-        <v>109179</v>
+        <v>120051</v>
       </c>
       <c r="J95" t="s">
         <v>564</v>
@@ -5770,12 +5770,12 @@
         <v>656</v>
       </c>
       <c r="L95" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96">
-        <v>212</v>
+        <v>412</v>
       </c>
       <c r="B96" t="s">
         <v>15</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97">
-        <v>268</v>
+        <v>468</v>
       </c>
       <c r="B97" t="s">
         <v>15</v>
@@ -5822,12 +5822,12 @@
         <v>656</v>
       </c>
       <c r="L97" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98">
-        <v>265</v>
+        <v>465</v>
       </c>
       <c r="B98" t="s">
         <v>15</v>
@@ -5848,12 +5848,12 @@
         <v>656</v>
       </c>
       <c r="L98" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99">
-        <v>216</v>
+        <v>416</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
@@ -5874,12 +5874,12 @@
         <v>656</v>
       </c>
       <c r="L99" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100">
-        <v>276</v>
+        <v>476</v>
       </c>
       <c r="B100" t="s">
         <v>15</v>
@@ -5900,12 +5900,12 @@
         <v>656</v>
       </c>
       <c r="L100" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101">
-        <v>257</v>
+        <v>457</v>
       </c>
       <c r="B101" t="s">
         <v>15</v>
@@ -5926,12 +5926,12 @@
         <v>656</v>
       </c>
       <c r="L101" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102">
-        <v>214</v>
+        <v>414</v>
       </c>
       <c r="B102" t="s">
         <v>15</v>
@@ -5957,7 +5957,7 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103">
-        <v>266</v>
+        <v>466</v>
       </c>
       <c r="B103" t="s">
         <v>15</v>
@@ -5978,12 +5978,12 @@
         <v>656</v>
       </c>
       <c r="L103" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104">
-        <v>267</v>
+        <v>467</v>
       </c>
       <c r="B104" t="s">
         <v>15</v>
@@ -6004,12 +6004,12 @@
         <v>656</v>
       </c>
       <c r="L104" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105">
-        <v>272</v>
+        <v>472</v>
       </c>
       <c r="B105" t="s">
         <v>15</v>
@@ -6030,12 +6030,12 @@
         <v>656</v>
       </c>
       <c r="L105" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106">
-        <v>273</v>
+        <v>473</v>
       </c>
       <c r="B106" t="s">
         <v>15</v>
@@ -6056,12 +6056,12 @@
         <v>656</v>
       </c>
       <c r="L106" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107">
-        <v>269</v>
+        <v>469</v>
       </c>
       <c r="B107" t="s">
         <v>15</v>
@@ -6082,12 +6082,12 @@
         <v>656</v>
       </c>
       <c r="L107" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108">
-        <v>270</v>
+        <v>470</v>
       </c>
       <c r="B108" t="s">
         <v>15</v>
@@ -6108,12 +6108,12 @@
         <v>656</v>
       </c>
       <c r="L108" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109">
-        <v>271</v>
+        <v>471</v>
       </c>
       <c r="B109" t="s">
         <v>15</v>
@@ -6134,12 +6134,12 @@
         <v>656</v>
       </c>
       <c r="L109" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110">
-        <v>377</v>
+        <v>577</v>
       </c>
       <c r="B110" t="s">
         <v>16</v>
@@ -6160,7 +6160,7 @@
         <v>513</v>
       </c>
       <c r="H110">
-        <v>118503</v>
+        <v>129375</v>
       </c>
       <c r="I110">
         <v>5</v>
@@ -6177,7 +6177,7 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111">
-        <v>203</v>
+        <v>403</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
@@ -6206,7 +6206,7 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112">
-        <v>207</v>
+        <v>407</v>
       </c>
       <c r="B112" t="s">
         <v>15</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113">
-        <v>315</v>
+        <v>515</v>
       </c>
       <c r="B113" t="s">
         <v>16</v>
@@ -6256,7 +6256,7 @@
         <v>514</v>
       </c>
       <c r="H113">
-        <v>109005</v>
+        <v>119877</v>
       </c>
       <c r="I113">
         <v>6</v>
@@ -6268,12 +6268,12 @@
         <v>656</v>
       </c>
       <c r="L113" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114">
-        <v>206</v>
+        <v>406</v>
       </c>
       <c r="B114" t="s">
         <v>15</v>
@@ -6302,7 +6302,7 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115">
-        <v>329</v>
+        <v>529</v>
       </c>
       <c r="B115" t="s">
         <v>16</v>
@@ -6323,7 +6323,7 @@
         <v>462</v>
       </c>
       <c r="H115">
-        <v>111639</v>
+        <v>122511</v>
       </c>
       <c r="I115">
         <v>7</v>
@@ -6335,12 +6335,12 @@
         <v>656</v>
       </c>
       <c r="L115" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116">
-        <v>210</v>
+        <v>410</v>
       </c>
       <c r="B116" t="s">
         <v>15</v>
@@ -6369,7 +6369,7 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117">
-        <v>242</v>
+        <v>442</v>
       </c>
       <c r="B117" t="s">
         <v>15</v>
@@ -6393,12 +6393,12 @@
         <v>656</v>
       </c>
       <c r="L117" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118">
-        <v>241</v>
+        <v>441</v>
       </c>
       <c r="B118" t="s">
         <v>15</v>
@@ -6422,12 +6422,12 @@
         <v>656</v>
       </c>
       <c r="L118" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119">
-        <v>218</v>
+        <v>418</v>
       </c>
       <c r="B119" t="s">
         <v>15</v>
@@ -6451,12 +6451,12 @@
         <v>656</v>
       </c>
       <c r="L119" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120">
-        <v>208</v>
+        <v>408</v>
       </c>
       <c r="B120" t="s">
         <v>15</v>
@@ -6485,7 +6485,7 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121">
-        <v>223</v>
+        <v>423</v>
       </c>
       <c r="B121" t="s">
         <v>15</v>
@@ -6509,12 +6509,12 @@
         <v>656</v>
       </c>
       <c r="L121" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122">
-        <v>217</v>
+        <v>417</v>
       </c>
       <c r="B122" t="s">
         <v>15</v>
@@ -6538,12 +6538,12 @@
         <v>656</v>
       </c>
       <c r="L122" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123">
-        <v>209</v>
+        <v>409</v>
       </c>
       <c r="B123" t="s">
         <v>15</v>
@@ -6572,7 +6572,7 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124">
-        <v>211</v>
+        <v>411</v>
       </c>
       <c r="B124" t="s">
         <v>15</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125">
-        <v>274</v>
+        <v>474</v>
       </c>
       <c r="B125" t="s">
         <v>15</v>
@@ -6625,12 +6625,12 @@
         <v>656</v>
       </c>
       <c r="L125" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="126" spans="1:12">
       <c r="A126">
-        <v>283</v>
+        <v>483</v>
       </c>
       <c r="B126" t="s">
         <v>15</v>
@@ -6654,12 +6654,12 @@
         <v>656</v>
       </c>
       <c r="L126" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127">
-        <v>243</v>
+        <v>443</v>
       </c>
       <c r="B127" t="s">
         <v>15</v>
@@ -6683,12 +6683,12 @@
         <v>656</v>
       </c>
       <c r="L127" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128">
-        <v>221</v>
+        <v>421</v>
       </c>
       <c r="B128" t="s">
         <v>15</v>
@@ -6712,12 +6712,12 @@
         <v>656</v>
       </c>
       <c r="L128" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="129" spans="1:12">
       <c r="A129">
-        <v>219</v>
+        <v>419</v>
       </c>
       <c r="B129" t="s">
         <v>15</v>
@@ -6741,12 +6741,12 @@
         <v>656</v>
       </c>
       <c r="L129" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130">
-        <v>204</v>
+        <v>404</v>
       </c>
       <c r="B130" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131">
-        <v>288</v>
+        <v>488</v>
       </c>
       <c r="B131" t="s">
         <v>15</v>
@@ -6799,12 +6799,12 @@
         <v>656</v>
       </c>
       <c r="L131" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="132" spans="1:12">
       <c r="A132">
-        <v>297</v>
+        <v>497</v>
       </c>
       <c r="B132" t="s">
         <v>15</v>
@@ -6828,12 +6828,12 @@
         <v>656</v>
       </c>
       <c r="L132" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="133" spans="1:12">
       <c r="A133">
-        <v>228</v>
+        <v>428</v>
       </c>
       <c r="B133" t="s">
         <v>15</v>
@@ -6857,12 +6857,12 @@
         <v>656</v>
       </c>
       <c r="L133" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="134" spans="1:12">
       <c r="A134">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="B134" t="s">
         <v>15</v>
@@ -6886,12 +6886,12 @@
         <v>656</v>
       </c>
       <c r="L134" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="135" spans="1:12">
       <c r="A135">
-        <v>238</v>
+        <v>438</v>
       </c>
       <c r="B135" t="s">
         <v>15</v>
@@ -6915,12 +6915,12 @@
         <v>656</v>
       </c>
       <c r="L135" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="136" spans="1:12">
       <c r="A136">
-        <v>247</v>
+        <v>447</v>
       </c>
       <c r="B136" t="s">
         <v>15</v>
@@ -6944,12 +6944,12 @@
         <v>656</v>
       </c>
       <c r="L136" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="137" spans="1:12">
       <c r="A137">
-        <v>222</v>
+        <v>422</v>
       </c>
       <c r="B137" t="s">
         <v>15</v>
@@ -6973,12 +6973,12 @@
         <v>656</v>
       </c>
       <c r="L137" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="138" spans="1:12">
       <c r="A138">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="B138" t="s">
         <v>15</v>
@@ -7002,12 +7002,12 @@
         <v>656</v>
       </c>
       <c r="L138" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="139" spans="1:12">
       <c r="A139">
-        <v>249</v>
+        <v>449</v>
       </c>
       <c r="B139" t="s">
         <v>15</v>
@@ -7031,12 +7031,12 @@
         <v>656</v>
       </c>
       <c r="L139" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="140" spans="1:12">
       <c r="A140">
-        <v>213</v>
+        <v>413</v>
       </c>
       <c r="B140" t="s">
         <v>15</v>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141">
-        <v>224</v>
+        <v>424</v>
       </c>
       <c r="B141" t="s">
         <v>15</v>
@@ -7089,12 +7089,12 @@
         <v>656</v>
       </c>
       <c r="L141" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="142" spans="1:12">
       <c r="A142">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="B142" t="s">
         <v>15</v>
@@ -7118,12 +7118,12 @@
         <v>656</v>
       </c>
       <c r="L142" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143">
-        <v>226</v>
+        <v>426</v>
       </c>
       <c r="B143" t="s">
         <v>15</v>
@@ -7147,12 +7147,12 @@
         <v>656</v>
       </c>
       <c r="L143" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="144" spans="1:12">
       <c r="A144">
-        <v>227</v>
+        <v>427</v>
       </c>
       <c r="B144" t="s">
         <v>15</v>
@@ -7176,12 +7176,12 @@
         <v>656</v>
       </c>
       <c r="L144" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="145" spans="1:12">
       <c r="A145">
-        <v>232</v>
+        <v>432</v>
       </c>
       <c r="B145" t="s">
         <v>15</v>
@@ -7205,12 +7205,12 @@
         <v>656</v>
       </c>
       <c r="L145" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="146" spans="1:12">
       <c r="A146">
-        <v>310</v>
+        <v>510</v>
       </c>
       <c r="B146" t="s">
         <v>15</v>
@@ -7234,12 +7234,12 @@
         <v>656</v>
       </c>
       <c r="L146" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="147" spans="1:12">
       <c r="A147">
-        <v>244</v>
+        <v>444</v>
       </c>
       <c r="B147" t="s">
         <v>15</v>
@@ -7263,12 +7263,12 @@
         <v>656</v>
       </c>
       <c r="L147" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="148" spans="1:12">
       <c r="A148">
-        <v>246</v>
+        <v>446</v>
       </c>
       <c r="B148" t="s">
         <v>15</v>
@@ -7292,12 +7292,12 @@
         <v>656</v>
       </c>
       <c r="L148" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="149" spans="1:12">
       <c r="A149">
-        <v>282</v>
+        <v>482</v>
       </c>
       <c r="B149" t="s">
         <v>15</v>
@@ -7321,12 +7321,12 @@
         <v>656</v>
       </c>
       <c r="L149" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="150" spans="1:12">
       <c r="A150">
-        <v>230</v>
+        <v>430</v>
       </c>
       <c r="B150" t="s">
         <v>15</v>
@@ -7350,12 +7350,12 @@
         <v>656</v>
       </c>
       <c r="L150" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="151" spans="1:12">
       <c r="A151">
-        <v>312</v>
+        <v>512</v>
       </c>
       <c r="B151" t="s">
         <v>15</v>
@@ -7379,12 +7379,12 @@
         <v>656</v>
       </c>
       <c r="L151" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="152" spans="1:12">
       <c r="A152">
-        <v>307</v>
+        <v>507</v>
       </c>
       <c r="B152" t="s">
         <v>15</v>
@@ -7408,12 +7408,12 @@
         <v>656</v>
       </c>
       <c r="L152" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="153" spans="1:12">
       <c r="A153">
-        <v>293</v>
+        <v>493</v>
       </c>
       <c r="B153" t="s">
         <v>15</v>
@@ -7437,12 +7437,12 @@
         <v>656</v>
       </c>
       <c r="L153" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="154" spans="1:12">
       <c r="A154">
-        <v>313</v>
+        <v>513</v>
       </c>
       <c r="B154" t="s">
         <v>15</v>
@@ -7466,12 +7466,12 @@
         <v>656</v>
       </c>
       <c r="L154" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="155" spans="1:12">
       <c r="A155">
-        <v>237</v>
+        <v>437</v>
       </c>
       <c r="B155" t="s">
         <v>15</v>
@@ -7495,12 +7495,12 @@
         <v>656</v>
       </c>
       <c r="L155" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="156" spans="1:12">
       <c r="A156">
-        <v>231</v>
+        <v>431</v>
       </c>
       <c r="B156" t="s">
         <v>15</v>
@@ -7524,12 +7524,12 @@
         <v>656</v>
       </c>
       <c r="L156" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="157" spans="1:12">
       <c r="A157">
-        <v>309</v>
+        <v>509</v>
       </c>
       <c r="B157" t="s">
         <v>15</v>
@@ -7553,12 +7553,12 @@
         <v>656</v>
       </c>
       <c r="L157" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="158" spans="1:12">
       <c r="A158">
-        <v>277</v>
+        <v>477</v>
       </c>
       <c r="B158" t="s">
         <v>15</v>
@@ -7582,12 +7582,12 @@
         <v>656</v>
       </c>
       <c r="L158" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159">
-        <v>308</v>
+        <v>508</v>
       </c>
       <c r="B159" t="s">
         <v>15</v>
@@ -7611,12 +7611,12 @@
         <v>656</v>
       </c>
       <c r="L159" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="160" spans="1:12">
       <c r="A160">
-        <v>296</v>
+        <v>496</v>
       </c>
       <c r="B160" t="s">
         <v>15</v>
@@ -7640,12 +7640,12 @@
         <v>656</v>
       </c>
       <c r="L160" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="161" spans="1:12">
       <c r="A161">
-        <v>311</v>
+        <v>511</v>
       </c>
       <c r="B161" t="s">
         <v>15</v>
@@ -7669,12 +7669,12 @@
         <v>656</v>
       </c>
       <c r="L161" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="162" spans="1:12">
       <c r="A162">
-        <v>291</v>
+        <v>491</v>
       </c>
       <c r="B162" t="s">
         <v>15</v>
@@ -7698,12 +7698,12 @@
         <v>656</v>
       </c>
       <c r="L162" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="163" spans="1:12">
       <c r="A163">
-        <v>306</v>
+        <v>506</v>
       </c>
       <c r="B163" t="s">
         <v>15</v>
@@ -7727,12 +7727,12 @@
         <v>656</v>
       </c>
       <c r="L163" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="164" spans="1:12">
       <c r="A164">
-        <v>253</v>
+        <v>453</v>
       </c>
       <c r="B164" t="s">
         <v>15</v>
@@ -7756,12 +7756,12 @@
         <v>656</v>
       </c>
       <c r="L164" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="165" spans="1:12">
       <c r="A165">
-        <v>205</v>
+        <v>405</v>
       </c>
       <c r="B165" t="s">
         <v>15</v>
@@ -7790,7 +7790,7 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166">
-        <v>290</v>
+        <v>490</v>
       </c>
       <c r="B166" t="s">
         <v>15</v>
@@ -7814,12 +7814,12 @@
         <v>656</v>
       </c>
       <c r="L166" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="167" spans="1:12">
       <c r="A167">
-        <v>254</v>
+        <v>454</v>
       </c>
       <c r="B167" t="s">
         <v>15</v>
@@ -7843,12 +7843,12 @@
         <v>656</v>
       </c>
       <c r="L167" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="168" spans="1:12">
       <c r="A168">
-        <v>245</v>
+        <v>445</v>
       </c>
       <c r="B168" t="s">
         <v>15</v>
@@ -7872,12 +7872,12 @@
         <v>656</v>
       </c>
       <c r="L168" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="169" spans="1:12">
       <c r="A169">
-        <v>233</v>
+        <v>433</v>
       </c>
       <c r="B169" t="s">
         <v>15</v>
@@ -7901,12 +7901,12 @@
         <v>656</v>
       </c>
       <c r="L169" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="170" spans="1:12">
       <c r="A170">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="B170" t="s">
         <v>15</v>
@@ -7930,12 +7930,12 @@
         <v>656</v>
       </c>
       <c r="L170" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="171" spans="1:12">
       <c r="A171">
-        <v>302</v>
+        <v>502</v>
       </c>
       <c r="B171" t="s">
         <v>15</v>
@@ -7959,12 +7959,12 @@
         <v>656</v>
       </c>
       <c r="L171" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="172" spans="1:12">
       <c r="A172">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="B172" t="s">
         <v>15</v>
@@ -7988,12 +7988,12 @@
         <v>656</v>
       </c>
       <c r="L172" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="173" spans="1:12">
       <c r="A173">
-        <v>235</v>
+        <v>435</v>
       </c>
       <c r="B173" t="s">
         <v>15</v>
@@ -8017,12 +8017,12 @@
         <v>656</v>
       </c>
       <c r="L173" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="174" spans="1:12">
       <c r="A174">
-        <v>259</v>
+        <v>459</v>
       </c>
       <c r="B174" t="s">
         <v>15</v>
@@ -8046,12 +8046,12 @@
         <v>656</v>
       </c>
       <c r="L174" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="175" spans="1:12">
       <c r="A175">
-        <v>263</v>
+        <v>463</v>
       </c>
       <c r="B175" t="s">
         <v>15</v>
@@ -8075,12 +8075,12 @@
         <v>656</v>
       </c>
       <c r="L175" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="176" spans="1:12">
       <c r="A176">
-        <v>289</v>
+        <v>489</v>
       </c>
       <c r="B176" t="s">
         <v>15</v>
@@ -8104,12 +8104,12 @@
         <v>656</v>
       </c>
       <c r="L176" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="177" spans="1:12">
       <c r="A177">
-        <v>285</v>
+        <v>485</v>
       </c>
       <c r="B177" t="s">
         <v>15</v>
@@ -8133,12 +8133,12 @@
         <v>656</v>
       </c>
       <c r="L177" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="178" spans="1:12">
       <c r="A178">
-        <v>234</v>
+        <v>434</v>
       </c>
       <c r="B178" t="s">
         <v>15</v>
@@ -8162,12 +8162,12 @@
         <v>656</v>
       </c>
       <c r="L178" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="179" spans="1:12">
       <c r="A179">
-        <v>229</v>
+        <v>429</v>
       </c>
       <c r="B179" t="s">
         <v>15</v>
@@ -8191,12 +8191,12 @@
         <v>656</v>
       </c>
       <c r="L179" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="180" spans="1:12">
       <c r="A180">
-        <v>260</v>
+        <v>460</v>
       </c>
       <c r="B180" t="s">
         <v>15</v>
@@ -8220,12 +8220,12 @@
         <v>656</v>
       </c>
       <c r="L180" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="181" spans="1:12">
       <c r="A181">
-        <v>264</v>
+        <v>464</v>
       </c>
       <c r="B181" t="s">
         <v>15</v>
@@ -8249,12 +8249,12 @@
         <v>656</v>
       </c>
       <c r="L181" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="182" spans="1:12">
       <c r="A182">
-        <v>286</v>
+        <v>486</v>
       </c>
       <c r="B182" t="s">
         <v>15</v>
@@ -8278,12 +8278,12 @@
         <v>656</v>
       </c>
       <c r="L182" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="183" spans="1:12">
       <c r="A183">
-        <v>284</v>
+        <v>484</v>
       </c>
       <c r="B183" t="s">
         <v>15</v>
@@ -8307,12 +8307,12 @@
         <v>656</v>
       </c>
       <c r="L183" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="184" spans="1:12">
       <c r="A184">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="B184" t="s">
         <v>15</v>
@@ -8336,12 +8336,12 @@
         <v>656</v>
       </c>
       <c r="L184" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="185" spans="1:12">
       <c r="A185">
-        <v>299</v>
+        <v>499</v>
       </c>
       <c r="B185" t="s">
         <v>15</v>
@@ -8365,12 +8365,12 @@
         <v>656</v>
       </c>
       <c r="L185" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="186" spans="1:12">
       <c r="A186">
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="B186" t="s">
         <v>15</v>
@@ -8394,12 +8394,12 @@
         <v>656</v>
       </c>
       <c r="L186" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="187" spans="1:12">
       <c r="A187">
-        <v>305</v>
+        <v>505</v>
       </c>
       <c r="B187" t="s">
         <v>15</v>
@@ -8423,12 +8423,12 @@
         <v>656</v>
       </c>
       <c r="L187" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="188" spans="1:12">
       <c r="A188">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="B188" t="s">
         <v>15</v>
@@ -8452,12 +8452,12 @@
         <v>656</v>
       </c>
       <c r="L188" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="189" spans="1:12">
       <c r="A189">
-        <v>239</v>
+        <v>439</v>
       </c>
       <c r="B189" t="s">
         <v>15</v>
@@ -8481,12 +8481,12 @@
         <v>656</v>
       </c>
       <c r="L189" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="190" spans="1:12">
       <c r="A190">
-        <v>278</v>
+        <v>478</v>
       </c>
       <c r="B190" t="s">
         <v>15</v>
@@ -8510,12 +8510,12 @@
         <v>656</v>
       </c>
       <c r="L190" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="191" spans="1:12">
       <c r="A191">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="B191" t="s">
         <v>15</v>
@@ -8539,12 +8539,12 @@
         <v>656</v>
       </c>
       <c r="L191" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="192" spans="1:12">
       <c r="A192">
-        <v>236</v>
+        <v>436</v>
       </c>
       <c r="B192" t="s">
         <v>15</v>
@@ -8568,12 +8568,12 @@
         <v>656</v>
       </c>
       <c r="L192" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="193" spans="1:12">
       <c r="A193">
-        <v>261</v>
+        <v>461</v>
       </c>
       <c r="B193" t="s">
         <v>15</v>
@@ -8597,12 +8597,12 @@
         <v>656</v>
       </c>
       <c r="L193" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="194" spans="1:12">
       <c r="A194">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="B194" t="s">
         <v>15</v>
@@ -8626,12 +8626,12 @@
         <v>656</v>
       </c>
       <c r="L194" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="195" spans="1:12">
       <c r="A195">
-        <v>248</v>
+        <v>448</v>
       </c>
       <c r="B195" t="s">
         <v>15</v>
@@ -8655,12 +8655,12 @@
         <v>656</v>
       </c>
       <c r="L195" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="196" spans="1:12">
       <c r="A196">
-        <v>255</v>
+        <v>455</v>
       </c>
       <c r="B196" t="s">
         <v>15</v>
@@ -8684,12 +8684,12 @@
         <v>656</v>
       </c>
       <c r="L196" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="197" spans="1:12">
       <c r="A197">
-        <v>251</v>
+        <v>451</v>
       </c>
       <c r="B197" t="s">
         <v>15</v>
@@ -8713,12 +8713,12 @@
         <v>656</v>
       </c>
       <c r="L197" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="198" spans="1:12">
       <c r="A198">
-        <v>256</v>
+        <v>456</v>
       </c>
       <c r="B198" t="s">
         <v>15</v>
@@ -8742,12 +8742,12 @@
         <v>656</v>
       </c>
       <c r="L198" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="199" spans="1:12">
       <c r="A199">
-        <v>279</v>
+        <v>479</v>
       </c>
       <c r="B199" t="s">
         <v>15</v>
@@ -8771,12 +8771,12 @@
         <v>656</v>
       </c>
       <c r="L199" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="200" spans="1:12">
       <c r="A200">
-        <v>252</v>
+        <v>452</v>
       </c>
       <c r="B200" t="s">
         <v>15</v>
@@ -8800,12 +8800,12 @@
         <v>656</v>
       </c>
       <c r="L200" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="201" spans="1:12">
       <c r="A201">
-        <v>298</v>
+        <v>498</v>
       </c>
       <c r="B201" t="s">
         <v>15</v>
@@ -8829,7 +8829,7 @@
         <v>656</v>
       </c>
       <c r="L201" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/relationship_validation.xlsx
+++ b/data/exports/relationship_validation.xlsx
@@ -1987,10 +1987,10 @@
     <t>open</t>
   </si>
   <si>
-    <t>2026-05-23 23:28:23</t>
-  </si>
-  <si>
-    <t>2026-05-23 23:28:22</t>
+    <t>2026-05-24 00:04:50</t>
+  </si>
+  <si>
+    <t>2026-05-24 00:04:49</t>
   </si>
 </sst>
 </file>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>596</v>
+        <v>996</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -2386,7 +2386,7 @@
         <v>201</v>
       </c>
       <c r="H2">
-        <v>130207</v>
+        <v>151951</v>
       </c>
       <c r="J2" t="s">
         <v>515</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>597</v>
+        <v>997</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -2421,7 +2421,7 @@
         <v>201</v>
       </c>
       <c r="H3">
-        <v>130215</v>
+        <v>151959</v>
       </c>
       <c r="J3" t="s">
         <v>515</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>527</v>
+        <v>927</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -2456,7 +2456,7 @@
         <v>446</v>
       </c>
       <c r="H4">
-        <v>121461</v>
+        <v>143205</v>
       </c>
       <c r="J4" t="s">
         <v>516</v>
@@ -2465,12 +2465,12 @@
         <v>656</v>
       </c>
       <c r="L4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>585</v>
+        <v>985</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -2491,7 +2491,7 @@
         <v>447</v>
       </c>
       <c r="H5">
-        <v>129815</v>
+        <v>151559</v>
       </c>
       <c r="J5" t="s">
         <v>517</v>
@@ -2500,12 +2500,12 @@
         <v>656</v>
       </c>
       <c r="L5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>520</v>
+        <v>920</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2526,7 +2526,7 @@
         <v>208</v>
       </c>
       <c r="H6">
-        <v>120053</v>
+        <v>141797</v>
       </c>
       <c r="J6" t="s">
         <v>518</v>
@@ -2535,12 +2535,12 @@
         <v>656</v>
       </c>
       <c r="L6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>518</v>
+        <v>918</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2561,7 +2561,7 @@
         <v>208</v>
       </c>
       <c r="H7">
-        <v>120051</v>
+        <v>141795</v>
       </c>
       <c r="J7" t="s">
         <v>519</v>
@@ -2570,12 +2570,12 @@
         <v>656</v>
       </c>
       <c r="L7" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>532</v>
+        <v>932</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -2596,7 +2596,7 @@
         <v>448</v>
       </c>
       <c r="H8">
-        <v>122701</v>
+        <v>144445</v>
       </c>
       <c r="J8" t="s">
         <v>520</v>
@@ -2605,12 +2605,12 @@
         <v>656</v>
       </c>
       <c r="L8" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>570</v>
+        <v>970</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -2631,7 +2631,7 @@
         <v>449</v>
       </c>
       <c r="H9">
-        <v>127973</v>
+        <v>149717</v>
       </c>
       <c r="J9" t="s">
         <v>521</v>
@@ -2640,12 +2640,12 @@
         <v>656</v>
       </c>
       <c r="L9" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>415</v>
+        <v>815</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>549</v>
+        <v>949</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2692,7 +2692,7 @@
         <v>450</v>
       </c>
       <c r="H11">
-        <v>125851</v>
+        <v>147595</v>
       </c>
       <c r="J11" t="s">
         <v>523</v>
@@ -2701,12 +2701,12 @@
         <v>656</v>
       </c>
       <c r="L11" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>550</v>
+        <v>950</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2727,7 +2727,7 @@
         <v>451</v>
       </c>
       <c r="H12">
-        <v>125855</v>
+        <v>147599</v>
       </c>
       <c r="J12" t="s">
         <v>524</v>
@@ -2736,12 +2736,12 @@
         <v>656</v>
       </c>
       <c r="L12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>551</v>
+        <v>951</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -2762,7 +2762,7 @@
         <v>452</v>
       </c>
       <c r="H13">
-        <v>125859</v>
+        <v>147603</v>
       </c>
       <c r="J13" t="s">
         <v>525</v>
@@ -2771,12 +2771,12 @@
         <v>656</v>
       </c>
       <c r="L13" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>552</v>
+        <v>952</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2797,7 +2797,7 @@
         <v>453</v>
       </c>
       <c r="H14">
-        <v>125863</v>
+        <v>147607</v>
       </c>
       <c r="J14" t="s">
         <v>526</v>
@@ -2806,12 +2806,12 @@
         <v>656</v>
       </c>
       <c r="L14" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>553</v>
+        <v>953</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2832,7 +2832,7 @@
         <v>454</v>
       </c>
       <c r="H15">
-        <v>125867</v>
+        <v>147611</v>
       </c>
       <c r="J15" t="s">
         <v>527</v>
@@ -2841,12 +2841,12 @@
         <v>656</v>
       </c>
       <c r="L15" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>562</v>
+        <v>962</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -2867,7 +2867,7 @@
         <v>455</v>
       </c>
       <c r="H16">
-        <v>127705</v>
+        <v>149449</v>
       </c>
       <c r="J16" t="s">
         <v>528</v>
@@ -2876,12 +2876,12 @@
         <v>656</v>
       </c>
       <c r="L16" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17">
-        <v>563</v>
+        <v>963</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -2902,7 +2902,7 @@
         <v>456</v>
       </c>
       <c r="H17">
-        <v>127709</v>
+        <v>149453</v>
       </c>
       <c r="J17" t="s">
         <v>529</v>
@@ -2911,12 +2911,12 @@
         <v>656</v>
       </c>
       <c r="L17" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18">
-        <v>564</v>
+        <v>964</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -2937,7 +2937,7 @@
         <v>457</v>
       </c>
       <c r="H18">
-        <v>127713</v>
+        <v>149457</v>
       </c>
       <c r="J18" t="s">
         <v>530</v>
@@ -2946,12 +2946,12 @@
         <v>656</v>
       </c>
       <c r="L18" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19">
-        <v>565</v>
+        <v>965</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -2972,7 +2972,7 @@
         <v>458</v>
       </c>
       <c r="H19">
-        <v>127717</v>
+        <v>149461</v>
       </c>
       <c r="J19" t="s">
         <v>531</v>
@@ -2981,12 +2981,12 @@
         <v>656</v>
       </c>
       <c r="L19" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20">
-        <v>566</v>
+        <v>966</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3007,7 +3007,7 @@
         <v>459</v>
       </c>
       <c r="H20">
-        <v>127721</v>
+        <v>149465</v>
       </c>
       <c r="J20" t="s">
         <v>532</v>
@@ -3016,12 +3016,12 @@
         <v>656</v>
       </c>
       <c r="L20" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21">
-        <v>567</v>
+        <v>967</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3042,7 +3042,7 @@
         <v>460</v>
       </c>
       <c r="H21">
-        <v>127725</v>
+        <v>149469</v>
       </c>
       <c r="J21" t="s">
         <v>533</v>
@@ -3051,12 +3051,12 @@
         <v>656</v>
       </c>
       <c r="L21" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22">
-        <v>524</v>
+        <v>924</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3077,7 +3077,7 @@
         <v>461</v>
       </c>
       <c r="H22">
-        <v>120719</v>
+        <v>142463</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -3089,12 +3089,12 @@
         <v>656</v>
       </c>
       <c r="L22" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23">
-        <v>530</v>
+        <v>930</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3115,7 +3115,7 @@
         <v>462</v>
       </c>
       <c r="H23">
-        <v>122513</v>
+        <v>144257</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -3127,12 +3127,12 @@
         <v>656</v>
       </c>
       <c r="L23" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24">
-        <v>540</v>
+        <v>940</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -3153,7 +3153,7 @@
         <v>463</v>
       </c>
       <c r="H24">
-        <v>123901</v>
+        <v>145645</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -3165,12 +3165,12 @@
         <v>656</v>
       </c>
       <c r="L24" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25">
-        <v>539</v>
+        <v>939</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -3191,7 +3191,7 @@
         <v>464</v>
       </c>
       <c r="H25">
-        <v>123757</v>
+        <v>145501</v>
       </c>
       <c r="I25">
         <v>8</v>
@@ -3203,12 +3203,12 @@
         <v>656</v>
       </c>
       <c r="L25" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26">
-        <v>548</v>
+        <v>948</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3229,7 +3229,7 @@
         <v>465</v>
       </c>
       <c r="H26">
-        <v>125121</v>
+        <v>146865</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -3241,12 +3241,12 @@
         <v>656</v>
       </c>
       <c r="L26" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27">
-        <v>593</v>
+        <v>993</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
@@ -3267,7 +3267,7 @@
         <v>466</v>
       </c>
       <c r="H27">
-        <v>130149</v>
+        <v>151893</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28">
-        <v>547</v>
+        <v>947</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3305,7 +3305,7 @@
         <v>465</v>
       </c>
       <c r="H28">
-        <v>125119</v>
+        <v>146863</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -3317,12 +3317,12 @@
         <v>656</v>
       </c>
       <c r="L28" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29">
-        <v>574</v>
+        <v>974</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -3343,7 +3343,7 @@
         <v>467</v>
       </c>
       <c r="H29">
-        <v>129011</v>
+        <v>150755</v>
       </c>
       <c r="I29">
         <v>9</v>
@@ -3355,12 +3355,12 @@
         <v>656</v>
       </c>
       <c r="L29" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30">
-        <v>514</v>
+        <v>914</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -3381,7 +3381,7 @@
         <v>468</v>
       </c>
       <c r="H30">
-        <v>119719</v>
+        <v>141463</v>
       </c>
       <c r="I30">
         <v>9</v>
@@ -3393,12 +3393,12 @@
         <v>656</v>
       </c>
       <c r="L30" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31">
-        <v>554</v>
+        <v>954</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -3419,7 +3419,7 @@
         <v>469</v>
       </c>
       <c r="H31">
-        <v>126005</v>
+        <v>147749</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -3431,12 +3431,12 @@
         <v>656</v>
       </c>
       <c r="L31" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32">
-        <v>546</v>
+        <v>946</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -3457,7 +3457,7 @@
         <v>470</v>
       </c>
       <c r="H32">
-        <v>125079</v>
+        <v>146823</v>
       </c>
       <c r="I32">
         <v>9</v>
@@ -3469,12 +3469,12 @@
         <v>656</v>
       </c>
       <c r="L32" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33">
-        <v>581</v>
+        <v>981</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -3495,7 +3495,7 @@
         <v>470</v>
       </c>
       <c r="H33">
-        <v>129597</v>
+        <v>151341</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3507,12 +3507,12 @@
         <v>656</v>
       </c>
       <c r="L33" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34">
-        <v>573</v>
+        <v>973</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -3533,7 +3533,7 @@
         <v>467</v>
       </c>
       <c r="H34">
-        <v>129009</v>
+        <v>150753</v>
       </c>
       <c r="I34">
         <v>9</v>
@@ -3545,12 +3545,12 @@
         <v>656</v>
       </c>
       <c r="L34" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35">
-        <v>525</v>
+        <v>925</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -3571,7 +3571,7 @@
         <v>471</v>
       </c>
       <c r="H35">
-        <v>121221</v>
+        <v>142965</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -3583,12 +3583,12 @@
         <v>656</v>
       </c>
       <c r="L35" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36">
-        <v>545</v>
+        <v>945</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -3609,7 +3609,7 @@
         <v>470</v>
       </c>
       <c r="H36">
-        <v>125077</v>
+        <v>146821</v>
       </c>
       <c r="I36">
         <v>9</v>
@@ -3621,12 +3621,12 @@
         <v>656</v>
       </c>
       <c r="L36" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37">
-        <v>602</v>
+        <v>1002</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3647,7 +3647,7 @@
         <v>472</v>
       </c>
       <c r="H37">
-        <v>130391</v>
+        <v>152135</v>
       </c>
       <c r="I37">
         <v>10</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38">
-        <v>572</v>
+        <v>972</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -3685,7 +3685,7 @@
         <v>473</v>
       </c>
       <c r="H38">
-        <v>128987</v>
+        <v>150731</v>
       </c>
       <c r="I38">
         <v>11</v>
@@ -3697,12 +3697,12 @@
         <v>656</v>
       </c>
       <c r="L38" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39">
-        <v>544</v>
+        <v>944</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -3723,7 +3723,7 @@
         <v>474</v>
       </c>
       <c r="H39">
-        <v>124535</v>
+        <v>146279</v>
       </c>
       <c r="I39">
         <v>11</v>
@@ -3735,12 +3735,12 @@
         <v>656</v>
       </c>
       <c r="L39" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40">
-        <v>560</v>
+        <v>960</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -3761,7 +3761,7 @@
         <v>475</v>
       </c>
       <c r="H40">
-        <v>126513</v>
+        <v>148257</v>
       </c>
       <c r="I40">
         <v>11</v>
@@ -3773,12 +3773,12 @@
         <v>656</v>
       </c>
       <c r="L40" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41">
-        <v>584</v>
+        <v>984</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -3799,7 +3799,7 @@
         <v>476</v>
       </c>
       <c r="H41">
-        <v>129761</v>
+        <v>151505</v>
       </c>
       <c r="I41">
         <v>11</v>
@@ -3811,12 +3811,12 @@
         <v>656</v>
       </c>
       <c r="L41" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42">
-        <v>569</v>
+        <v>969</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
@@ -3837,7 +3837,7 @@
         <v>477</v>
       </c>
       <c r="H42">
-        <v>127871</v>
+        <v>149615</v>
       </c>
       <c r="I42">
         <v>12</v>
@@ -3849,12 +3849,12 @@
         <v>656</v>
       </c>
       <c r="L42" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43">
-        <v>521</v>
+        <v>921</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
@@ -3875,7 +3875,7 @@
         <v>478</v>
       </c>
       <c r="H43">
-        <v>120087</v>
+        <v>141831</v>
       </c>
       <c r="I43">
         <v>12</v>
@@ -3887,12 +3887,12 @@
         <v>656</v>
       </c>
       <c r="L43" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44">
-        <v>543</v>
+        <v>943</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
@@ -3913,7 +3913,7 @@
         <v>479</v>
       </c>
       <c r="H44">
-        <v>124433</v>
+        <v>146177</v>
       </c>
       <c r="I44">
         <v>12</v>
@@ -3925,12 +3925,12 @@
         <v>656</v>
       </c>
       <c r="L44" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45">
-        <v>568</v>
+        <v>968</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -3951,7 +3951,7 @@
         <v>480</v>
       </c>
       <c r="H45">
-        <v>127731</v>
+        <v>149475</v>
       </c>
       <c r="I45">
         <v>12</v>
@@ -3963,12 +3963,12 @@
         <v>656</v>
       </c>
       <c r="L45" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46">
-        <v>592</v>
+        <v>992</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -3989,7 +3989,7 @@
         <v>481</v>
       </c>
       <c r="H46">
-        <v>130073</v>
+        <v>151817</v>
       </c>
       <c r="I46">
         <v>13</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47">
-        <v>598</v>
+        <v>998</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -4027,7 +4027,7 @@
         <v>235</v>
       </c>
       <c r="H47">
-        <v>130247</v>
+        <v>151991</v>
       </c>
       <c r="I47">
         <v>13</v>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48">
-        <v>523</v>
+        <v>923</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4065,7 +4065,7 @@
         <v>482</v>
       </c>
       <c r="H48">
-        <v>120529</v>
+        <v>142273</v>
       </c>
       <c r="I48">
         <v>13</v>
@@ -4077,12 +4077,12 @@
         <v>656</v>
       </c>
       <c r="L48" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49">
-        <v>555</v>
+        <v>955</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
@@ -4103,7 +4103,7 @@
         <v>483</v>
       </c>
       <c r="H49">
-        <v>126117</v>
+        <v>147861</v>
       </c>
       <c r="I49">
         <v>13</v>
@@ -4115,12 +4115,12 @@
         <v>656</v>
       </c>
       <c r="L49" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50">
-        <v>528</v>
+        <v>928</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
@@ -4141,7 +4141,7 @@
         <v>484</v>
       </c>
       <c r="H50">
-        <v>121753</v>
+        <v>143497</v>
       </c>
       <c r="I50">
         <v>13</v>
@@ -4153,12 +4153,12 @@
         <v>656</v>
       </c>
       <c r="L50" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51">
-        <v>542</v>
+        <v>942</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
@@ -4179,7 +4179,7 @@
         <v>239</v>
       </c>
       <c r="H51">
-        <v>124399</v>
+        <v>146143</v>
       </c>
       <c r="I51">
         <v>13</v>
@@ -4191,12 +4191,12 @@
         <v>656</v>
       </c>
       <c r="L51" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52">
-        <v>587</v>
+        <v>987</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
@@ -4217,7 +4217,7 @@
         <v>485</v>
       </c>
       <c r="H52">
-        <v>129895</v>
+        <v>151639</v>
       </c>
       <c r="I52">
         <v>13</v>
@@ -4229,12 +4229,12 @@
         <v>656</v>
       </c>
       <c r="L52" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53">
-        <v>586</v>
+        <v>986</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
@@ -4255,7 +4255,7 @@
         <v>486</v>
       </c>
       <c r="H53">
-        <v>129819</v>
+        <v>151563</v>
       </c>
       <c r="I53">
         <v>13</v>
@@ -4267,12 +4267,12 @@
         <v>656</v>
       </c>
       <c r="L53" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54">
-        <v>601</v>
+        <v>1001</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
@@ -4293,7 +4293,7 @@
         <v>487</v>
       </c>
       <c r="H54">
-        <v>130345</v>
+        <v>152089</v>
       </c>
       <c r="I54">
         <v>14</v>
@@ -4310,7 +4310,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55">
-        <v>558</v>
+        <v>958</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
@@ -4331,7 +4331,7 @@
         <v>488</v>
       </c>
       <c r="H55">
-        <v>126361</v>
+        <v>148105</v>
       </c>
       <c r="I55">
         <v>14</v>
@@ -4343,12 +4343,12 @@
         <v>656</v>
       </c>
       <c r="L55" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56">
-        <v>582</v>
+        <v>982</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
@@ -4369,7 +4369,7 @@
         <v>489</v>
       </c>
       <c r="H56">
-        <v>129653</v>
+        <v>151397</v>
       </c>
       <c r="I56">
         <v>14</v>
@@ -4381,12 +4381,12 @@
         <v>656</v>
       </c>
       <c r="L56" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57">
-        <v>559</v>
+        <v>959</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
@@ -4407,7 +4407,7 @@
         <v>490</v>
       </c>
       <c r="H57">
-        <v>126413</v>
+        <v>148157</v>
       </c>
       <c r="I57">
         <v>14</v>
@@ -4419,12 +4419,12 @@
         <v>656</v>
       </c>
       <c r="L57" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58">
-        <v>533</v>
+        <v>933</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
@@ -4445,7 +4445,7 @@
         <v>491</v>
       </c>
       <c r="H58">
-        <v>123057</v>
+        <v>144801</v>
       </c>
       <c r="I58">
         <v>14</v>
@@ -4457,12 +4457,12 @@
         <v>656</v>
       </c>
       <c r="L58" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59">
-        <v>538</v>
+        <v>938</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
@@ -4483,7 +4483,7 @@
         <v>492</v>
       </c>
       <c r="H59">
-        <v>123741</v>
+        <v>145485</v>
       </c>
       <c r="I59">
         <v>14</v>
@@ -4495,12 +4495,12 @@
         <v>656</v>
       </c>
       <c r="L59" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60">
-        <v>531</v>
+        <v>931</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4521,7 +4521,7 @@
         <v>493</v>
       </c>
       <c r="H60">
-        <v>122607</v>
+        <v>144351</v>
       </c>
       <c r="I60">
         <v>14</v>
@@ -4533,12 +4533,12 @@
         <v>656</v>
       </c>
       <c r="L60" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61">
-        <v>534</v>
+        <v>934</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
@@ -4559,7 +4559,7 @@
         <v>491</v>
       </c>
       <c r="H61">
-        <v>123059</v>
+        <v>144803</v>
       </c>
       <c r="I61">
         <v>14</v>
@@ -4571,12 +4571,12 @@
         <v>656</v>
       </c>
       <c r="L61" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62">
-        <v>588</v>
+        <v>988</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
@@ -4597,7 +4597,7 @@
         <v>494</v>
       </c>
       <c r="H62">
-        <v>129919</v>
+        <v>151663</v>
       </c>
       <c r="I62">
         <v>14</v>
@@ -4609,12 +4609,12 @@
         <v>656</v>
       </c>
       <c r="L62" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63">
-        <v>580</v>
+        <v>980</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
@@ -4635,7 +4635,7 @@
         <v>251</v>
       </c>
       <c r="H63">
-        <v>129551</v>
+        <v>151295</v>
       </c>
       <c r="I63">
         <v>14</v>
@@ -4647,12 +4647,12 @@
         <v>656</v>
       </c>
       <c r="L63" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64">
-        <v>571</v>
+        <v>971</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
@@ -4673,7 +4673,7 @@
         <v>495</v>
       </c>
       <c r="H64">
-        <v>128803</v>
+        <v>150547</v>
       </c>
       <c r="I64">
         <v>14</v>
@@ -4685,12 +4685,12 @@
         <v>656</v>
       </c>
       <c r="L64" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65">
-        <v>557</v>
+        <v>957</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
@@ -4711,7 +4711,7 @@
         <v>496</v>
       </c>
       <c r="H65">
-        <v>126141</v>
+        <v>147885</v>
       </c>
       <c r="I65">
         <v>15</v>
@@ -4723,12 +4723,12 @@
         <v>656</v>
       </c>
       <c r="L65" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66">
-        <v>575</v>
+        <v>975</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
@@ -4749,7 +4749,7 @@
         <v>497</v>
       </c>
       <c r="H66">
-        <v>129109</v>
+        <v>150853</v>
       </c>
       <c r="I66">
         <v>15</v>
@@ -4761,12 +4761,12 @@
         <v>656</v>
       </c>
       <c r="L66" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67">
-        <v>537</v>
+        <v>937</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
@@ -4787,7 +4787,7 @@
         <v>498</v>
       </c>
       <c r="H67">
-        <v>123711</v>
+        <v>145455</v>
       </c>
       <c r="I67">
         <v>15</v>
@@ -4799,12 +4799,12 @@
         <v>656</v>
       </c>
       <c r="L67" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68">
-        <v>522</v>
+        <v>922</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
@@ -4825,7 +4825,7 @@
         <v>499</v>
       </c>
       <c r="H68">
-        <v>120489</v>
+        <v>142233</v>
       </c>
       <c r="I68">
         <v>15</v>
@@ -4837,12 +4837,12 @@
         <v>656</v>
       </c>
       <c r="L68" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69">
-        <v>535</v>
+        <v>935</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -4863,7 +4863,7 @@
         <v>246</v>
       </c>
       <c r="H69">
-        <v>123103</v>
+        <v>144847</v>
       </c>
       <c r="I69">
         <v>15</v>
@@ -4875,12 +4875,12 @@
         <v>656</v>
       </c>
       <c r="L69" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70">
-        <v>526</v>
+        <v>926</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -4901,7 +4901,7 @@
         <v>500</v>
       </c>
       <c r="H70">
-        <v>121447</v>
+        <v>143191</v>
       </c>
       <c r="I70">
         <v>15</v>
@@ -4913,12 +4913,12 @@
         <v>656</v>
       </c>
       <c r="L70" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71">
-        <v>578</v>
+        <v>978</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
@@ -4939,7 +4939,7 @@
         <v>501</v>
       </c>
       <c r="H71">
-        <v>129455</v>
+        <v>151199</v>
       </c>
       <c r="I71">
         <v>15</v>
@@ -4951,12 +4951,12 @@
         <v>656</v>
       </c>
       <c r="L71" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72">
-        <v>594</v>
+        <v>994</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
@@ -4977,7 +4977,7 @@
         <v>502</v>
       </c>
       <c r="H72">
-        <v>130169</v>
+        <v>151913</v>
       </c>
       <c r="I72">
         <v>15</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73">
-        <v>536</v>
+        <v>936</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
@@ -5015,7 +5015,7 @@
         <v>503</v>
       </c>
       <c r="H73">
-        <v>123535</v>
+        <v>145279</v>
       </c>
       <c r="I73">
         <v>15</v>
@@ -5027,12 +5027,12 @@
         <v>656</v>
       </c>
       <c r="L73" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74">
-        <v>590</v>
+        <v>990</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -5053,7 +5053,7 @@
         <v>504</v>
       </c>
       <c r="H74">
-        <v>129963</v>
+        <v>151707</v>
       </c>
       <c r="I74">
         <v>15</v>
@@ -5065,12 +5065,12 @@
         <v>656</v>
       </c>
       <c r="L74" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75">
-        <v>556</v>
+        <v>956</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
@@ -5091,7 +5091,7 @@
         <v>496</v>
       </c>
       <c r="H75">
-        <v>126139</v>
+        <v>147883</v>
       </c>
       <c r="I75">
         <v>15</v>
@@ -5103,12 +5103,12 @@
         <v>656</v>
       </c>
       <c r="L75" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76">
-        <v>541</v>
+        <v>941</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
@@ -5129,7 +5129,7 @@
         <v>505</v>
       </c>
       <c r="H76">
-        <v>124233</v>
+        <v>145977</v>
       </c>
       <c r="I76">
         <v>15</v>
@@ -5141,12 +5141,12 @@
         <v>656</v>
       </c>
       <c r="L76" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77">
-        <v>561</v>
+        <v>961</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
@@ -5167,7 +5167,7 @@
         <v>506</v>
       </c>
       <c r="H77">
-        <v>126763</v>
+        <v>148507</v>
       </c>
       <c r="I77">
         <v>15</v>
@@ -5179,12 +5179,12 @@
         <v>656</v>
       </c>
       <c r="L77" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78">
-        <v>576</v>
+        <v>976</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
@@ -5205,7 +5205,7 @@
         <v>507</v>
       </c>
       <c r="H78">
-        <v>129289</v>
+        <v>151033</v>
       </c>
       <c r="I78">
         <v>16</v>
@@ -5217,12 +5217,12 @@
         <v>656</v>
       </c>
       <c r="L78" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
@@ -5243,7 +5243,7 @@
         <v>508</v>
       </c>
       <c r="H79">
-        <v>130337</v>
+        <v>152081</v>
       </c>
       <c r="I79">
         <v>16</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80">
-        <v>599</v>
+        <v>999</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
@@ -5281,7 +5281,7 @@
         <v>509</v>
       </c>
       <c r="H80">
-        <v>130325</v>
+        <v>152069</v>
       </c>
       <c r="I80">
         <v>16</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81">
-        <v>583</v>
+        <v>983</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
@@ -5319,7 +5319,7 @@
         <v>510</v>
       </c>
       <c r="H81">
-        <v>129727</v>
+        <v>151471</v>
       </c>
       <c r="I81">
         <v>16</v>
@@ -5331,12 +5331,12 @@
         <v>656</v>
       </c>
       <c r="L81" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82">
-        <v>579</v>
+        <v>979</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
@@ -5357,7 +5357,7 @@
         <v>267</v>
       </c>
       <c r="H82">
-        <v>129489</v>
+        <v>151233</v>
       </c>
       <c r="I82">
         <v>17</v>
@@ -5369,12 +5369,12 @@
         <v>656</v>
       </c>
       <c r="L82" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83">
-        <v>591</v>
+        <v>991</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
@@ -5395,7 +5395,7 @@
         <v>511</v>
       </c>
       <c r="H83">
-        <v>130051</v>
+        <v>151795</v>
       </c>
       <c r="I83">
         <v>17</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84">
-        <v>595</v>
+        <v>995</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
@@ -5433,7 +5433,7 @@
         <v>511</v>
       </c>
       <c r="H84">
-        <v>130177</v>
+        <v>151921</v>
       </c>
       <c r="I84">
         <v>17</v>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85">
-        <v>589</v>
+        <v>989</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
@@ -5471,7 +5471,7 @@
         <v>267</v>
       </c>
       <c r="H85">
-        <v>129957</v>
+        <v>151701</v>
       </c>
       <c r="I85">
         <v>18</v>
@@ -5483,12 +5483,12 @@
         <v>656</v>
       </c>
       <c r="L85" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86">
-        <v>475</v>
+        <v>875</v>
       </c>
       <c r="B86" t="s">
         <v>15</v>
@@ -5509,12 +5509,12 @@
         <v>656</v>
       </c>
       <c r="L86" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87">
-        <v>494</v>
+        <v>894</v>
       </c>
       <c r="B87" t="s">
         <v>15</v>
@@ -5535,12 +5535,12 @@
         <v>656</v>
       </c>
       <c r="L87" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88">
-        <v>516</v>
+        <v>916</v>
       </c>
       <c r="B88" t="s">
         <v>16</v>
@@ -5561,7 +5561,7 @@
         <v>512</v>
       </c>
       <c r="H88">
-        <v>119937</v>
+        <v>141681</v>
       </c>
       <c r="J88" t="s">
         <v>557</v>
@@ -5570,12 +5570,12 @@
         <v>656</v>
       </c>
       <c r="L88" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89">
-        <v>503</v>
+        <v>903</v>
       </c>
       <c r="B89" t="s">
         <v>15</v>
@@ -5596,12 +5596,12 @@
         <v>656</v>
       </c>
       <c r="L89" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90">
-        <v>504</v>
+        <v>904</v>
       </c>
       <c r="B90" t="s">
         <v>15</v>
@@ -5622,12 +5622,12 @@
         <v>656</v>
       </c>
       <c r="L90" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91">
-        <v>519</v>
+        <v>919</v>
       </c>
       <c r="B91" t="s">
         <v>16</v>
@@ -5648,7 +5648,7 @@
         <v>208</v>
       </c>
       <c r="H91">
-        <v>120053</v>
+        <v>141797</v>
       </c>
       <c r="J91" t="s">
         <v>560</v>
@@ -5657,12 +5657,12 @@
         <v>656</v>
       </c>
       <c r="L91" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92">
-        <v>458</v>
+        <v>858</v>
       </c>
       <c r="B92" t="s">
         <v>15</v>
@@ -5683,12 +5683,12 @@
         <v>656</v>
       </c>
       <c r="L92" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93">
-        <v>492</v>
+        <v>892</v>
       </c>
       <c r="B93" t="s">
         <v>15</v>
@@ -5709,12 +5709,12 @@
         <v>656</v>
       </c>
       <c r="L93" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94">
-        <v>487</v>
+        <v>887</v>
       </c>
       <c r="B94" t="s">
         <v>15</v>
@@ -5735,12 +5735,12 @@
         <v>656</v>
       </c>
       <c r="L94" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95">
-        <v>517</v>
+        <v>917</v>
       </c>
       <c r="B95" t="s">
         <v>16</v>
@@ -5761,7 +5761,7 @@
         <v>208</v>
       </c>
       <c r="H95">
-        <v>120051</v>
+        <v>141795</v>
       </c>
       <c r="J95" t="s">
         <v>564</v>
@@ -5770,12 +5770,12 @@
         <v>656</v>
       </c>
       <c r="L95" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96">
-        <v>412</v>
+        <v>812</v>
       </c>
       <c r="B96" t="s">
         <v>15</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97">
-        <v>468</v>
+        <v>868</v>
       </c>
       <c r="B97" t="s">
         <v>15</v>
@@ -5822,12 +5822,12 @@
         <v>656</v>
       </c>
       <c r="L97" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98">
-        <v>465</v>
+        <v>865</v>
       </c>
       <c r="B98" t="s">
         <v>15</v>
@@ -5848,12 +5848,12 @@
         <v>656</v>
       </c>
       <c r="L98" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99">
-        <v>416</v>
+        <v>816</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
@@ -5874,12 +5874,12 @@
         <v>656</v>
       </c>
       <c r="L99" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100">
-        <v>476</v>
+        <v>876</v>
       </c>
       <c r="B100" t="s">
         <v>15</v>
@@ -5900,12 +5900,12 @@
         <v>656</v>
       </c>
       <c r="L100" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101">
-        <v>457</v>
+        <v>857</v>
       </c>
       <c r="B101" t="s">
         <v>15</v>
@@ -5926,12 +5926,12 @@
         <v>656</v>
       </c>
       <c r="L101" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102">
-        <v>414</v>
+        <v>814</v>
       </c>
       <c r="B102" t="s">
         <v>15</v>
@@ -5957,7 +5957,7 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103">
-        <v>466</v>
+        <v>866</v>
       </c>
       <c r="B103" t="s">
         <v>15</v>
@@ -5978,12 +5978,12 @@
         <v>656</v>
       </c>
       <c r="L103" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104">
-        <v>467</v>
+        <v>867</v>
       </c>
       <c r="B104" t="s">
         <v>15</v>
@@ -6004,12 +6004,12 @@
         <v>656</v>
       </c>
       <c r="L104" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105">
-        <v>472</v>
+        <v>872</v>
       </c>
       <c r="B105" t="s">
         <v>15</v>
@@ -6030,12 +6030,12 @@
         <v>656</v>
       </c>
       <c r="L105" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106">
-        <v>473</v>
+        <v>873</v>
       </c>
       <c r="B106" t="s">
         <v>15</v>
@@ -6056,12 +6056,12 @@
         <v>656</v>
       </c>
       <c r="L106" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107">
-        <v>469</v>
+        <v>869</v>
       </c>
       <c r="B107" t="s">
         <v>15</v>
@@ -6082,12 +6082,12 @@
         <v>656</v>
       </c>
       <c r="L107" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108">
-        <v>470</v>
+        <v>870</v>
       </c>
       <c r="B108" t="s">
         <v>15</v>
@@ -6108,12 +6108,12 @@
         <v>656</v>
       </c>
       <c r="L108" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109">
-        <v>471</v>
+        <v>871</v>
       </c>
       <c r="B109" t="s">
         <v>15</v>
@@ -6134,12 +6134,12 @@
         <v>656</v>
       </c>
       <c r="L109" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110">
-        <v>577</v>
+        <v>977</v>
       </c>
       <c r="B110" t="s">
         <v>16</v>
@@ -6160,7 +6160,7 @@
         <v>513</v>
       </c>
       <c r="H110">
-        <v>129375</v>
+        <v>151119</v>
       </c>
       <c r="I110">
         <v>5</v>
@@ -6172,12 +6172,12 @@
         <v>656</v>
       </c>
       <c r="L110" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111">
-        <v>403</v>
+        <v>803</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
@@ -6206,7 +6206,7 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112">
-        <v>407</v>
+        <v>807</v>
       </c>
       <c r="B112" t="s">
         <v>15</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113">
-        <v>515</v>
+        <v>915</v>
       </c>
       <c r="B113" t="s">
         <v>16</v>
@@ -6256,7 +6256,7 @@
         <v>514</v>
       </c>
       <c r="H113">
-        <v>119877</v>
+        <v>141621</v>
       </c>
       <c r="I113">
         <v>6</v>
@@ -6268,12 +6268,12 @@
         <v>656</v>
       </c>
       <c r="L113" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114">
-        <v>406</v>
+        <v>806</v>
       </c>
       <c r="B114" t="s">
         <v>15</v>
@@ -6302,7 +6302,7 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115">
-        <v>529</v>
+        <v>929</v>
       </c>
       <c r="B115" t="s">
         <v>16</v>
@@ -6323,7 +6323,7 @@
         <v>462</v>
       </c>
       <c r="H115">
-        <v>122511</v>
+        <v>144255</v>
       </c>
       <c r="I115">
         <v>7</v>
@@ -6335,12 +6335,12 @@
         <v>656</v>
       </c>
       <c r="L115" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116">
-        <v>410</v>
+        <v>810</v>
       </c>
       <c r="B116" t="s">
         <v>15</v>
@@ -6369,7 +6369,7 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117">
-        <v>442</v>
+        <v>842</v>
       </c>
       <c r="B117" t="s">
         <v>15</v>
@@ -6393,12 +6393,12 @@
         <v>656</v>
       </c>
       <c r="L117" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118">
-        <v>441</v>
+        <v>841</v>
       </c>
       <c r="B118" t="s">
         <v>15</v>
@@ -6422,12 +6422,12 @@
         <v>656</v>
       </c>
       <c r="L118" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119">
-        <v>418</v>
+        <v>818</v>
       </c>
       <c r="B119" t="s">
         <v>15</v>
@@ -6451,12 +6451,12 @@
         <v>656</v>
       </c>
       <c r="L119" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120">
-        <v>408</v>
+        <v>808</v>
       </c>
       <c r="B120" t="s">
         <v>15</v>
@@ -6485,7 +6485,7 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121">
-        <v>423</v>
+        <v>823</v>
       </c>
       <c r="B121" t="s">
         <v>15</v>
@@ -6509,12 +6509,12 @@
         <v>656</v>
       </c>
       <c r="L121" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122">
-        <v>417</v>
+        <v>817</v>
       </c>
       <c r="B122" t="s">
         <v>15</v>
@@ -6538,12 +6538,12 @@
         <v>656</v>
       </c>
       <c r="L122" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123">
-        <v>409</v>
+        <v>809</v>
       </c>
       <c r="B123" t="s">
         <v>15</v>
@@ -6572,7 +6572,7 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124">
-        <v>411</v>
+        <v>811</v>
       </c>
       <c r="B124" t="s">
         <v>15</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125">
-        <v>474</v>
+        <v>874</v>
       </c>
       <c r="B125" t="s">
         <v>15</v>
@@ -6625,12 +6625,12 @@
         <v>656</v>
       </c>
       <c r="L125" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="126" spans="1:12">
       <c r="A126">
-        <v>483</v>
+        <v>883</v>
       </c>
       <c r="B126" t="s">
         <v>15</v>
@@ -6654,12 +6654,12 @@
         <v>656</v>
       </c>
       <c r="L126" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127">
-        <v>443</v>
+        <v>843</v>
       </c>
       <c r="B127" t="s">
         <v>15</v>
@@ -6683,12 +6683,12 @@
         <v>656</v>
       </c>
       <c r="L127" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128">
-        <v>421</v>
+        <v>821</v>
       </c>
       <c r="B128" t="s">
         <v>15</v>
@@ -6712,12 +6712,12 @@
         <v>656</v>
       </c>
       <c r="L128" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="129" spans="1:12">
       <c r="A129">
-        <v>419</v>
+        <v>819</v>
       </c>
       <c r="B129" t="s">
         <v>15</v>
@@ -6741,12 +6741,12 @@
         <v>656</v>
       </c>
       <c r="L129" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130">
-        <v>404</v>
+        <v>804</v>
       </c>
       <c r="B130" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131">
-        <v>488</v>
+        <v>888</v>
       </c>
       <c r="B131" t="s">
         <v>15</v>
@@ -6799,12 +6799,12 @@
         <v>656</v>
       </c>
       <c r="L131" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="132" spans="1:12">
       <c r="A132">
-        <v>497</v>
+        <v>897</v>
       </c>
       <c r="B132" t="s">
         <v>15</v>
@@ -6828,12 +6828,12 @@
         <v>656</v>
       </c>
       <c r="L132" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="133" spans="1:12">
       <c r="A133">
-        <v>428</v>
+        <v>828</v>
       </c>
       <c r="B133" t="s">
         <v>15</v>
@@ -6857,12 +6857,12 @@
         <v>656</v>
       </c>
       <c r="L133" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="134" spans="1:12">
       <c r="A134">
-        <v>462</v>
+        <v>862</v>
       </c>
       <c r="B134" t="s">
         <v>15</v>
@@ -6886,12 +6886,12 @@
         <v>656</v>
       </c>
       <c r="L134" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="135" spans="1:12">
       <c r="A135">
-        <v>438</v>
+        <v>838</v>
       </c>
       <c r="B135" t="s">
         <v>15</v>
@@ -6915,12 +6915,12 @@
         <v>656</v>
       </c>
       <c r="L135" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="136" spans="1:12">
       <c r="A136">
-        <v>447</v>
+        <v>847</v>
       </c>
       <c r="B136" t="s">
         <v>15</v>
@@ -6944,12 +6944,12 @@
         <v>656</v>
       </c>
       <c r="L136" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="137" spans="1:12">
       <c r="A137">
-        <v>422</v>
+        <v>822</v>
       </c>
       <c r="B137" t="s">
         <v>15</v>
@@ -6973,12 +6973,12 @@
         <v>656</v>
       </c>
       <c r="L137" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="138" spans="1:12">
       <c r="A138">
-        <v>481</v>
+        <v>881</v>
       </c>
       <c r="B138" t="s">
         <v>15</v>
@@ -7002,12 +7002,12 @@
         <v>656</v>
       </c>
       <c r="L138" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="139" spans="1:12">
       <c r="A139">
-        <v>449</v>
+        <v>849</v>
       </c>
       <c r="B139" t="s">
         <v>15</v>
@@ -7031,12 +7031,12 @@
         <v>656</v>
       </c>
       <c r="L139" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="140" spans="1:12">
       <c r="A140">
-        <v>413</v>
+        <v>813</v>
       </c>
       <c r="B140" t="s">
         <v>15</v>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141">
-        <v>424</v>
+        <v>824</v>
       </c>
       <c r="B141" t="s">
         <v>15</v>
@@ -7089,12 +7089,12 @@
         <v>656</v>
       </c>
       <c r="L141" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="142" spans="1:12">
       <c r="A142">
-        <v>425</v>
+        <v>825</v>
       </c>
       <c r="B142" t="s">
         <v>15</v>
@@ -7118,12 +7118,12 @@
         <v>656</v>
       </c>
       <c r="L142" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143">
-        <v>426</v>
+        <v>826</v>
       </c>
       <c r="B143" t="s">
         <v>15</v>
@@ -7147,12 +7147,12 @@
         <v>656</v>
       </c>
       <c r="L143" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="144" spans="1:12">
       <c r="A144">
-        <v>427</v>
+        <v>827</v>
       </c>
       <c r="B144" t="s">
         <v>15</v>
@@ -7176,12 +7176,12 @@
         <v>656</v>
       </c>
       <c r="L144" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="145" spans="1:12">
       <c r="A145">
-        <v>432</v>
+        <v>832</v>
       </c>
       <c r="B145" t="s">
         <v>15</v>
@@ -7205,12 +7205,12 @@
         <v>656</v>
       </c>
       <c r="L145" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="146" spans="1:12">
       <c r="A146">
-        <v>510</v>
+        <v>910</v>
       </c>
       <c r="B146" t="s">
         <v>15</v>
@@ -7234,12 +7234,12 @@
         <v>656</v>
       </c>
       <c r="L146" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="147" spans="1:12">
       <c r="A147">
-        <v>444</v>
+        <v>844</v>
       </c>
       <c r="B147" t="s">
         <v>15</v>
@@ -7263,12 +7263,12 @@
         <v>656</v>
       </c>
       <c r="L147" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="148" spans="1:12">
       <c r="A148">
-        <v>446</v>
+        <v>846</v>
       </c>
       <c r="B148" t="s">
         <v>15</v>
@@ -7292,12 +7292,12 @@
         <v>656</v>
       </c>
       <c r="L148" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="149" spans="1:12">
       <c r="A149">
-        <v>482</v>
+        <v>882</v>
       </c>
       <c r="B149" t="s">
         <v>15</v>
@@ -7321,12 +7321,12 @@
         <v>656</v>
       </c>
       <c r="L149" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="150" spans="1:12">
       <c r="A150">
-        <v>430</v>
+        <v>830</v>
       </c>
       <c r="B150" t="s">
         <v>15</v>
@@ -7350,12 +7350,12 @@
         <v>656</v>
       </c>
       <c r="L150" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="151" spans="1:12">
       <c r="A151">
-        <v>512</v>
+        <v>912</v>
       </c>
       <c r="B151" t="s">
         <v>15</v>
@@ -7379,12 +7379,12 @@
         <v>656</v>
       </c>
       <c r="L151" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="152" spans="1:12">
       <c r="A152">
-        <v>507</v>
+        <v>907</v>
       </c>
       <c r="B152" t="s">
         <v>15</v>
@@ -7408,12 +7408,12 @@
         <v>656</v>
       </c>
       <c r="L152" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="153" spans="1:12">
       <c r="A153">
-        <v>493</v>
+        <v>893</v>
       </c>
       <c r="B153" t="s">
         <v>15</v>
@@ -7437,12 +7437,12 @@
         <v>656</v>
       </c>
       <c r="L153" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="154" spans="1:12">
       <c r="A154">
-        <v>513</v>
+        <v>913</v>
       </c>
       <c r="B154" t="s">
         <v>15</v>
@@ -7466,12 +7466,12 @@
         <v>656</v>
       </c>
       <c r="L154" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="155" spans="1:12">
       <c r="A155">
-        <v>437</v>
+        <v>837</v>
       </c>
       <c r="B155" t="s">
         <v>15</v>
@@ -7495,12 +7495,12 @@
         <v>656</v>
       </c>
       <c r="L155" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="156" spans="1:12">
       <c r="A156">
-        <v>431</v>
+        <v>831</v>
       </c>
       <c r="B156" t="s">
         <v>15</v>
@@ -7524,12 +7524,12 @@
         <v>656</v>
       </c>
       <c r="L156" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="157" spans="1:12">
       <c r="A157">
-        <v>509</v>
+        <v>909</v>
       </c>
       <c r="B157" t="s">
         <v>15</v>
@@ -7553,12 +7553,12 @@
         <v>656</v>
       </c>
       <c r="L157" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="158" spans="1:12">
       <c r="A158">
-        <v>477</v>
+        <v>877</v>
       </c>
       <c r="B158" t="s">
         <v>15</v>
@@ -7582,12 +7582,12 @@
         <v>656</v>
       </c>
       <c r="L158" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159">
-        <v>508</v>
+        <v>908</v>
       </c>
       <c r="B159" t="s">
         <v>15</v>
@@ -7611,12 +7611,12 @@
         <v>656</v>
       </c>
       <c r="L159" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="160" spans="1:12">
       <c r="A160">
-        <v>496</v>
+        <v>896</v>
       </c>
       <c r="B160" t="s">
         <v>15</v>
@@ -7640,12 +7640,12 @@
         <v>656</v>
       </c>
       <c r="L160" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="161" spans="1:12">
       <c r="A161">
-        <v>511</v>
+        <v>911</v>
       </c>
       <c r="B161" t="s">
         <v>15</v>
@@ -7669,12 +7669,12 @@
         <v>656</v>
       </c>
       <c r="L161" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="162" spans="1:12">
       <c r="A162">
-        <v>491</v>
+        <v>891</v>
       </c>
       <c r="B162" t="s">
         <v>15</v>
@@ -7698,12 +7698,12 @@
         <v>656</v>
       </c>
       <c r="L162" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="163" spans="1:12">
       <c r="A163">
-        <v>506</v>
+        <v>906</v>
       </c>
       <c r="B163" t="s">
         <v>15</v>
@@ -7727,12 +7727,12 @@
         <v>656</v>
       </c>
       <c r="L163" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="164" spans="1:12">
       <c r="A164">
-        <v>453</v>
+        <v>853</v>
       </c>
       <c r="B164" t="s">
         <v>15</v>
@@ -7756,12 +7756,12 @@
         <v>656</v>
       </c>
       <c r="L164" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="165" spans="1:12">
       <c r="A165">
-        <v>405</v>
+        <v>805</v>
       </c>
       <c r="B165" t="s">
         <v>15</v>
@@ -7790,7 +7790,7 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166">
-        <v>490</v>
+        <v>890</v>
       </c>
       <c r="B166" t="s">
         <v>15</v>
@@ -7814,12 +7814,12 @@
         <v>656</v>
       </c>
       <c r="L166" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="167" spans="1:12">
       <c r="A167">
-        <v>454</v>
+        <v>854</v>
       </c>
       <c r="B167" t="s">
         <v>15</v>
@@ -7843,12 +7843,12 @@
         <v>656</v>
       </c>
       <c r="L167" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="168" spans="1:12">
       <c r="A168">
-        <v>445</v>
+        <v>845</v>
       </c>
       <c r="B168" t="s">
         <v>15</v>
@@ -7872,12 +7872,12 @@
         <v>656</v>
       </c>
       <c r="L168" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="169" spans="1:12">
       <c r="A169">
-        <v>433</v>
+        <v>833</v>
       </c>
       <c r="B169" t="s">
         <v>15</v>
@@ -7901,12 +7901,12 @@
         <v>656</v>
       </c>
       <c r="L169" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="170" spans="1:12">
       <c r="A170">
-        <v>480</v>
+        <v>880</v>
       </c>
       <c r="B170" t="s">
         <v>15</v>
@@ -7930,12 +7930,12 @@
         <v>656</v>
       </c>
       <c r="L170" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="171" spans="1:12">
       <c r="A171">
-        <v>502</v>
+        <v>902</v>
       </c>
       <c r="B171" t="s">
         <v>15</v>
@@ -7959,12 +7959,12 @@
         <v>656</v>
       </c>
       <c r="L171" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="172" spans="1:12">
       <c r="A172">
-        <v>501</v>
+        <v>901</v>
       </c>
       <c r="B172" t="s">
         <v>15</v>
@@ -7988,12 +7988,12 @@
         <v>656</v>
       </c>
       <c r="L172" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="173" spans="1:12">
       <c r="A173">
-        <v>435</v>
+        <v>835</v>
       </c>
       <c r="B173" t="s">
         <v>15</v>
@@ -8017,12 +8017,12 @@
         <v>656</v>
       </c>
       <c r="L173" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="174" spans="1:12">
       <c r="A174">
-        <v>459</v>
+        <v>859</v>
       </c>
       <c r="B174" t="s">
         <v>15</v>
@@ -8046,12 +8046,12 @@
         <v>656</v>
       </c>
       <c r="L174" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="175" spans="1:12">
       <c r="A175">
-        <v>463</v>
+        <v>863</v>
       </c>
       <c r="B175" t="s">
         <v>15</v>
@@ -8075,12 +8075,12 @@
         <v>656</v>
       </c>
       <c r="L175" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="176" spans="1:12">
       <c r="A176">
-        <v>489</v>
+        <v>889</v>
       </c>
       <c r="B176" t="s">
         <v>15</v>
@@ -8104,12 +8104,12 @@
         <v>656</v>
       </c>
       <c r="L176" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="177" spans="1:12">
       <c r="A177">
-        <v>485</v>
+        <v>885</v>
       </c>
       <c r="B177" t="s">
         <v>15</v>
@@ -8133,12 +8133,12 @@
         <v>656</v>
       </c>
       <c r="L177" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="178" spans="1:12">
       <c r="A178">
-        <v>434</v>
+        <v>834</v>
       </c>
       <c r="B178" t="s">
         <v>15</v>
@@ -8162,12 +8162,12 @@
         <v>656</v>
       </c>
       <c r="L178" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="179" spans="1:12">
       <c r="A179">
-        <v>429</v>
+        <v>829</v>
       </c>
       <c r="B179" t="s">
         <v>15</v>
@@ -8191,12 +8191,12 @@
         <v>656</v>
       </c>
       <c r="L179" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="180" spans="1:12">
       <c r="A180">
-        <v>460</v>
+        <v>860</v>
       </c>
       <c r="B180" t="s">
         <v>15</v>
@@ -8220,12 +8220,12 @@
         <v>656</v>
       </c>
       <c r="L180" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="181" spans="1:12">
       <c r="A181">
-        <v>464</v>
+        <v>864</v>
       </c>
       <c r="B181" t="s">
         <v>15</v>
@@ -8249,12 +8249,12 @@
         <v>656</v>
       </c>
       <c r="L181" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="182" spans="1:12">
       <c r="A182">
-        <v>486</v>
+        <v>886</v>
       </c>
       <c r="B182" t="s">
         <v>15</v>
@@ -8278,12 +8278,12 @@
         <v>656</v>
       </c>
       <c r="L182" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="183" spans="1:12">
       <c r="A183">
-        <v>484</v>
+        <v>884</v>
       </c>
       <c r="B183" t="s">
         <v>15</v>
@@ -8307,12 +8307,12 @@
         <v>656</v>
       </c>
       <c r="L183" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="184" spans="1:12">
       <c r="A184">
-        <v>495</v>
+        <v>895</v>
       </c>
       <c r="B184" t="s">
         <v>15</v>
@@ -8336,12 +8336,12 @@
         <v>656</v>
       </c>
       <c r="L184" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="185" spans="1:12">
       <c r="A185">
-        <v>499</v>
+        <v>899</v>
       </c>
       <c r="B185" t="s">
         <v>15</v>
@@ -8365,12 +8365,12 @@
         <v>656</v>
       </c>
       <c r="L185" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="186" spans="1:12">
       <c r="A186">
-        <v>420</v>
+        <v>820</v>
       </c>
       <c r="B186" t="s">
         <v>15</v>
@@ -8394,12 +8394,12 @@
         <v>656</v>
       </c>
       <c r="L186" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="187" spans="1:12">
       <c r="A187">
-        <v>505</v>
+        <v>905</v>
       </c>
       <c r="B187" t="s">
         <v>15</v>
@@ -8423,12 +8423,12 @@
         <v>656</v>
       </c>
       <c r="L187" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="188" spans="1:12">
       <c r="A188">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="B188" t="s">
         <v>15</v>
@@ -8452,12 +8452,12 @@
         <v>656</v>
       </c>
       <c r="L188" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="189" spans="1:12">
       <c r="A189">
-        <v>439</v>
+        <v>839</v>
       </c>
       <c r="B189" t="s">
         <v>15</v>
@@ -8481,12 +8481,12 @@
         <v>656</v>
       </c>
       <c r="L189" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="190" spans="1:12">
       <c r="A190">
-        <v>478</v>
+        <v>878</v>
       </c>
       <c r="B190" t="s">
         <v>15</v>
@@ -8510,12 +8510,12 @@
         <v>656</v>
       </c>
       <c r="L190" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="191" spans="1:12">
       <c r="A191">
-        <v>440</v>
+        <v>840</v>
       </c>
       <c r="B191" t="s">
         <v>15</v>
@@ -8539,12 +8539,12 @@
         <v>656</v>
       </c>
       <c r="L191" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="192" spans="1:12">
       <c r="A192">
-        <v>436</v>
+        <v>836</v>
       </c>
       <c r="B192" t="s">
         <v>15</v>
@@ -8568,12 +8568,12 @@
         <v>656</v>
       </c>
       <c r="L192" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="193" spans="1:12">
       <c r="A193">
-        <v>461</v>
+        <v>861</v>
       </c>
       <c r="B193" t="s">
         <v>15</v>
@@ -8597,12 +8597,12 @@
         <v>656</v>
       </c>
       <c r="L193" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="194" spans="1:12">
       <c r="A194">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="B194" t="s">
         <v>15</v>
@@ -8626,12 +8626,12 @@
         <v>656</v>
       </c>
       <c r="L194" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="195" spans="1:12">
       <c r="A195">
-        <v>448</v>
+        <v>848</v>
       </c>
       <c r="B195" t="s">
         <v>15</v>
@@ -8655,12 +8655,12 @@
         <v>656</v>
       </c>
       <c r="L195" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="196" spans="1:12">
       <c r="A196">
-        <v>455</v>
+        <v>855</v>
       </c>
       <c r="B196" t="s">
         <v>15</v>
@@ -8684,12 +8684,12 @@
         <v>656</v>
       </c>
       <c r="L196" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="197" spans="1:12">
       <c r="A197">
-        <v>451</v>
+        <v>851</v>
       </c>
       <c r="B197" t="s">
         <v>15</v>
@@ -8713,12 +8713,12 @@
         <v>656</v>
       </c>
       <c r="L197" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="198" spans="1:12">
       <c r="A198">
-        <v>456</v>
+        <v>856</v>
       </c>
       <c r="B198" t="s">
         <v>15</v>
@@ -8742,12 +8742,12 @@
         <v>656</v>
       </c>
       <c r="L198" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="199" spans="1:12">
       <c r="A199">
-        <v>479</v>
+        <v>879</v>
       </c>
       <c r="B199" t="s">
         <v>15</v>
@@ -8771,12 +8771,12 @@
         <v>656</v>
       </c>
       <c r="L199" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="200" spans="1:12">
       <c r="A200">
-        <v>452</v>
+        <v>852</v>
       </c>
       <c r="B200" t="s">
         <v>15</v>
@@ -8800,12 +8800,12 @@
         <v>656</v>
       </c>
       <c r="L200" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="201" spans="1:12">
       <c r="A201">
-        <v>498</v>
+        <v>898</v>
       </c>
       <c r="B201" t="s">
         <v>15</v>
@@ -8829,7 +8829,7 @@
         <v>656</v>
       </c>
       <c r="L201" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
